--- a/artfynd/A 55314-2024 artfynd.xlsx
+++ b/artfynd/A 55314-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121670532</v>
+        <v>121671163</v>
       </c>
       <c r="B2" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,48 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514314</v>
+        <v>514227</v>
       </c>
       <c r="R2" t="n">
-        <v>7023286</v>
+        <v>7023300</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -793,12 +779,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -816,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121671167</v>
+        <v>121666620</v>
       </c>
       <c r="B3" t="n">
-        <v>79697</v>
+        <v>57373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,34 +818,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514229</v>
+        <v>514538</v>
       </c>
       <c r="R3" t="n">
-        <v>7023329</v>
+        <v>7023126</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -902,6 +898,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -918,7 +939,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121667545</v>
+        <v>121666863</v>
       </c>
       <c r="B4" t="n">
         <v>78616</v>
@@ -958,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514742</v>
+        <v>514695</v>
       </c>
       <c r="R4" t="n">
-        <v>7023172</v>
+        <v>7023177</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1045,7 +1066,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121669055</v>
+        <v>121669887</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1090,10 +1111,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514434</v>
+        <v>514428</v>
       </c>
       <c r="R5" t="n">
-        <v>7023259</v>
+        <v>7023241</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1152,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121667243</v>
+        <v>121667163</v>
       </c>
       <c r="B6" t="n">
-        <v>79733</v>
+        <v>79732</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,21 +1189,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1254,7 +1275,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121667649</v>
+        <v>121667141</v>
       </c>
       <c r="B7" t="n">
         <v>79697</v>
@@ -1294,10 +1315,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514709</v>
+        <v>514636</v>
       </c>
       <c r="R7" t="n">
-        <v>7023250</v>
+        <v>7023234</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1356,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121666824</v>
+        <v>121667243</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
+        <v>79733</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,25 +1389,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1396,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514678</v>
+        <v>514636</v>
       </c>
       <c r="R8" t="n">
-        <v>7023186</v>
+        <v>7023234</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,31 +1463,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1483,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121667163</v>
+        <v>121668309</v>
       </c>
       <c r="B9" t="n">
-        <v>79732</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,20 +1491,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1523,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514636</v>
+        <v>514672</v>
       </c>
       <c r="R9" t="n">
-        <v>7023234</v>
+        <v>7023245</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,6 +1565,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1585,10 +1606,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121669062</v>
+        <v>121668931</v>
       </c>
       <c r="B10" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,39 +1622,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514434</v>
+        <v>514674</v>
       </c>
       <c r="R10" t="n">
-        <v>7023257</v>
+        <v>7023130</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1676,6 +1692,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1692,7 +1733,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121669887</v>
+        <v>121671072</v>
       </c>
       <c r="B11" t="n">
         <v>57357</v>
@@ -1737,10 +1778,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514428</v>
+        <v>514232</v>
       </c>
       <c r="R11" t="n">
-        <v>7023241</v>
+        <v>7023294</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1799,7 +1840,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121669094</v>
+        <v>121669034</v>
       </c>
       <c r="B12" t="n">
         <v>78616</v>
@@ -1839,10 +1880,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514711</v>
+        <v>514722</v>
       </c>
       <c r="R12" t="n">
-        <v>7023153</v>
+        <v>7023113</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1926,10 +1967,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121667138</v>
+        <v>121670797</v>
       </c>
       <c r="B13" t="n">
-        <v>78616</v>
+        <v>79698</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1942,34 +1983,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514735</v>
+        <v>514262</v>
       </c>
       <c r="R13" t="n">
-        <v>7023174</v>
+        <v>7023275</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2015,27 +2061,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2053,10 +2099,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121670772</v>
+        <v>121667142</v>
       </c>
       <c r="B14" t="n">
-        <v>79697</v>
+        <v>79698</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2069,34 +2115,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514217</v>
+        <v>514636</v>
       </c>
       <c r="R14" t="n">
-        <v>7023244</v>
+        <v>7023234</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2155,10 +2201,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121669034</v>
+        <v>121670753</v>
       </c>
       <c r="B15" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2171,34 +2217,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514722</v>
+        <v>514257</v>
       </c>
       <c r="R15" t="n">
-        <v>7023113</v>
+        <v>7023271</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2244,27 +2290,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Våtmark med barrträd</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2282,10 +2328,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121670773</v>
+        <v>121670799</v>
       </c>
       <c r="B16" t="n">
-        <v>79698</v>
+        <v>79726</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2294,38 +2340,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514216</v>
+        <v>514265</v>
       </c>
       <c r="R16" t="n">
-        <v>7023241</v>
+        <v>7023278</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2368,6 +2419,31 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2384,7 +2460,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121671125</v>
+        <v>121667649</v>
       </c>
       <c r="B17" t="n">
         <v>79697</v>
@@ -2418,21 +2494,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514222</v>
+        <v>514709</v>
       </c>
       <c r="R17" t="n">
-        <v>7023316</v>
+        <v>7023250</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2475,31 +2546,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2516,10 +2562,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121667143</v>
+        <v>121670504</v>
       </c>
       <c r="B18" t="n">
-        <v>79726</v>
+        <v>79697</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2528,38 +2574,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514636</v>
+        <v>514335</v>
       </c>
       <c r="R18" t="n">
-        <v>7023234</v>
+        <v>7023306</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2618,10 +2664,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121666863</v>
+        <v>121671167</v>
       </c>
       <c r="B19" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2634,34 +2680,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514695</v>
+        <v>514229</v>
       </c>
       <c r="R19" t="n">
-        <v>7023177</v>
+        <v>7023329</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2704,31 +2750,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2745,10 +2766,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121668931</v>
+        <v>121671149</v>
       </c>
       <c r="B20" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2761,34 +2782,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514674</v>
+        <v>514237</v>
       </c>
       <c r="R20" t="n">
-        <v>7023130</v>
+        <v>7023316</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2831,31 +2852,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2872,10 +2868,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121670504</v>
+        <v>121667138</v>
       </c>
       <c r="B21" t="n">
-        <v>79697</v>
+        <v>78616</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2888,34 +2884,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514335</v>
+        <v>514735</v>
       </c>
       <c r="R21" t="n">
-        <v>7023306</v>
+        <v>7023174</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2958,6 +2954,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2974,7 +2995,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121668309</v>
+        <v>121667545</v>
       </c>
       <c r="B22" t="n">
         <v>78616</v>
@@ -3014,10 +3035,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514672</v>
+        <v>514742</v>
       </c>
       <c r="R22" t="n">
-        <v>7023245</v>
+        <v>7023172</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3101,10 +3122,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121670797</v>
+        <v>121670772</v>
       </c>
       <c r="B23" t="n">
-        <v>79698</v>
+        <v>79697</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3117,39 +3138,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514262</v>
+        <v>514217</v>
       </c>
       <c r="R23" t="n">
-        <v>7023275</v>
+        <v>7023244</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3192,31 +3208,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3233,7 +3224,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121670753</v>
+        <v>121671125</v>
       </c>
       <c r="B24" t="n">
         <v>79697</v>
@@ -3267,16 +3258,21 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>514257</v>
+        <v>514222</v>
       </c>
       <c r="R24" t="n">
-        <v>7023271</v>
+        <v>7023316</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3322,7 +3318,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -3360,7 +3356,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121670575</v>
+        <v>121671097</v>
       </c>
       <c r="B25" t="n">
         <v>79697</v>
@@ -3394,16 +3390,21 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>514301</v>
+        <v>514216</v>
       </c>
       <c r="R25" t="n">
-        <v>7023286</v>
+        <v>7023328</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3446,6 +3447,31 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3462,10 +3488,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121671149</v>
+        <v>121670532</v>
       </c>
       <c r="B26" t="n">
-        <v>79697</v>
+        <v>90746</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3478,34 +3504,48 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>514237</v>
+        <v>514314</v>
       </c>
       <c r="R26" t="n">
-        <v>7023316</v>
+        <v>7023286</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3548,6 +3588,31 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3564,10 +3629,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121667141</v>
+        <v>121669062</v>
       </c>
       <c r="B27" t="n">
-        <v>79697</v>
+        <v>57357</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3580,34 +3645,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>514636</v>
+        <v>514434</v>
       </c>
       <c r="R27" t="n">
-        <v>7023234</v>
+        <v>7023257</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3666,10 +3736,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121671072</v>
+        <v>121667143</v>
       </c>
       <c r="B28" t="n">
-        <v>57357</v>
+        <v>79726</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3678,43 +3748,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>514232</v>
+        <v>514636</v>
       </c>
       <c r="R28" t="n">
-        <v>7023294</v>
+        <v>7023234</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3773,10 +3838,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121671163</v>
+        <v>121669055</v>
       </c>
       <c r="B29" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3789,34 +3854,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>514227</v>
+        <v>514434</v>
       </c>
       <c r="R29" t="n">
-        <v>7023300</v>
+        <v>7023259</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3859,31 +3929,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3900,10 +3945,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121667142</v>
+        <v>121669094</v>
       </c>
       <c r="B30" t="n">
-        <v>79698</v>
+        <v>78616</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3916,21 +3961,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3940,10 +3985,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514636</v>
+        <v>514711</v>
       </c>
       <c r="R30" t="n">
-        <v>7023234</v>
+        <v>7023153</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3986,6 +4031,31 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Våtmark med barrträd</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4002,10 +4072,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121670799</v>
+        <v>121666824</v>
       </c>
       <c r="B31" t="n">
-        <v>79726</v>
+        <v>78616</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4014,43 +4084,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>514265</v>
+        <v>514678</v>
       </c>
       <c r="R31" t="n">
-        <v>7023278</v>
+        <v>7023186</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4096,27 +4161,27 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4134,7 +4199,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121671169</v>
+        <v>121670773</v>
       </c>
       <c r="B32" t="n">
         <v>79698</v>
@@ -4174,10 +4239,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514228</v>
+        <v>514216</v>
       </c>
       <c r="R32" t="n">
-        <v>7023328</v>
+        <v>7023241</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4236,10 +4301,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121666620</v>
+        <v>121671169</v>
       </c>
       <c r="B33" t="n">
-        <v>57373</v>
+        <v>79698</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4252,44 +4317,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>514538</v>
+        <v>514228</v>
       </c>
       <c r="R33" t="n">
-        <v>7023126</v>
+        <v>7023328</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4332,31 +4387,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4373,7 +4403,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121671097</v>
+        <v>121670575</v>
       </c>
       <c r="B34" t="n">
         <v>79697</v>
@@ -4407,21 +4437,16 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514216</v>
+        <v>514301</v>
       </c>
       <c r="R34" t="n">
-        <v>7023328</v>
+        <v>7023286</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4464,31 +4489,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">

--- a/artfynd/A 55314-2024 artfynd.xlsx
+++ b/artfynd/A 55314-2024 artfynd.xlsx
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121666620</v>
+        <v>121669887</v>
       </c>
       <c r="B3" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -841,21 +841,16 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514538</v>
+        <v>514428</v>
       </c>
       <c r="R3" t="n">
-        <v>7023126</v>
+        <v>7023241</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,31 +893,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -939,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121666863</v>
+        <v>121666620</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -955,34 +925,44 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514695</v>
+        <v>514538</v>
       </c>
       <c r="R4" t="n">
-        <v>7023177</v>
+        <v>7023126</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1043,12 +1023,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1066,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121669887</v>
+        <v>121666863</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1082,39 +1062,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514428</v>
+        <v>514695</v>
       </c>
       <c r="R5" t="n">
-        <v>7023241</v>
+        <v>7023177</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1157,6 +1132,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -2099,10 +2099,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121667142</v>
+        <v>121670753</v>
       </c>
       <c r="B14" t="n">
-        <v>79698</v>
+        <v>79697</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2115,34 +2115,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514636</v>
+        <v>514257</v>
       </c>
       <c r="R14" t="n">
-        <v>7023234</v>
+        <v>7023271</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2185,6 +2185,31 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2201,10 +2226,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121670753</v>
+        <v>121670799</v>
       </c>
       <c r="B15" t="n">
-        <v>79697</v>
+        <v>79726</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2213,38 +2238,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514257</v>
+        <v>514265</v>
       </c>
       <c r="R15" t="n">
-        <v>7023271</v>
+        <v>7023278</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2328,10 +2358,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121670799</v>
+        <v>121667142</v>
       </c>
       <c r="B16" t="n">
-        <v>79726</v>
+        <v>79698</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2340,43 +2370,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514265</v>
+        <v>514636</v>
       </c>
       <c r="R16" t="n">
-        <v>7023278</v>
+        <v>7023234</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2419,31 +2444,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2995,10 +2995,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121667545</v>
+        <v>121670772</v>
       </c>
       <c r="B22" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3011,34 +3011,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514742</v>
+        <v>514217</v>
       </c>
       <c r="R22" t="n">
-        <v>7023172</v>
+        <v>7023244</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3081,31 +3081,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3122,10 +3097,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121670772</v>
+        <v>121667545</v>
       </c>
       <c r="B23" t="n">
-        <v>79697</v>
+        <v>78616</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3138,34 +3113,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514217</v>
+        <v>514742</v>
       </c>
       <c r="R23" t="n">
-        <v>7023244</v>
+        <v>7023172</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3208,6 +3183,31 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">

--- a/artfynd/A 55314-2024 artfynd.xlsx
+++ b/artfynd/A 55314-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121671163</v>
+        <v>121671125</v>
       </c>
       <c r="B2" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514227</v>
+        <v>514222</v>
       </c>
       <c r="R2" t="n">
-        <v>7023300</v>
+        <v>7023316</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,22 +774,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121669887</v>
+        <v>121667649</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
+        <v>79697</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,39 +823,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514428</v>
+        <v>514709</v>
       </c>
       <c r="R3" t="n">
-        <v>7023241</v>
+        <v>7023250</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121666620</v>
+        <v>121666863</v>
       </c>
       <c r="B4" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,44 +925,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514538</v>
+        <v>514695</v>
       </c>
       <c r="R4" t="n">
-        <v>7023126</v>
+        <v>7023177</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1023,12 +1013,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1046,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121666863</v>
+        <v>121671167</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,34 +1052,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514695</v>
+        <v>514229</v>
       </c>
       <c r="R5" t="n">
-        <v>7023177</v>
+        <v>7023329</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,31 +1122,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1173,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121667163</v>
+        <v>121667141</v>
       </c>
       <c r="B6" t="n">
-        <v>79732</v>
+        <v>79697</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1185,25 +1150,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1275,7 +1240,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121667141</v>
+        <v>121670753</v>
       </c>
       <c r="B7" t="n">
         <v>79697</v>
@@ -1311,14 +1276,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514636</v>
+        <v>514257</v>
       </c>
       <c r="R7" t="n">
-        <v>7023234</v>
+        <v>7023271</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1361,6 +1326,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1377,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121667243</v>
+        <v>121667545</v>
       </c>
       <c r="B8" t="n">
-        <v>79733</v>
+        <v>78616</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1389,25 +1379,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1417,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514636</v>
+        <v>514742</v>
       </c>
       <c r="R8" t="n">
-        <v>7023234</v>
+        <v>7023172</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1463,6 +1453,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1479,7 +1494,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121668309</v>
+        <v>121669094</v>
       </c>
       <c r="B9" t="n">
         <v>78616</v>
@@ -1519,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514672</v>
+        <v>514711</v>
       </c>
       <c r="R9" t="n">
-        <v>7023245</v>
+        <v>7023153</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,7 +1583,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Våtmark med barrträd</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1606,10 +1621,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121668931</v>
+        <v>121667143</v>
       </c>
       <c r="B10" t="n">
-        <v>78616</v>
+        <v>79726</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1618,25 +1633,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1646,10 +1661,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514674</v>
+        <v>514636</v>
       </c>
       <c r="R10" t="n">
-        <v>7023130</v>
+        <v>7023234</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1692,31 +1707,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1733,10 +1723,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121671072</v>
+        <v>121671149</v>
       </c>
       <c r="B11" t="n">
-        <v>57357</v>
+        <v>79697</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1749,39 +1739,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514232</v>
+        <v>514237</v>
       </c>
       <c r="R11" t="n">
-        <v>7023294</v>
+        <v>7023316</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1840,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121669034</v>
+        <v>121670504</v>
       </c>
       <c r="B12" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1856,34 +1841,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514722</v>
+        <v>514335</v>
       </c>
       <c r="R12" t="n">
-        <v>7023113</v>
+        <v>7023306</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1926,31 +1911,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Våtmark med barrträd</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1967,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121670797</v>
+        <v>121669887</v>
       </c>
       <c r="B13" t="n">
-        <v>79698</v>
+        <v>57357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1983,27 +1943,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2012,10 +1972,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514262</v>
+        <v>514428</v>
       </c>
       <c r="R13" t="n">
-        <v>7023275</v>
+        <v>7023241</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2058,31 +2018,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2099,10 +2034,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121670753</v>
+        <v>121671163</v>
       </c>
       <c r="B14" t="n">
-        <v>79697</v>
+        <v>78616</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2115,21 +2050,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2139,10 +2074,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514257</v>
+        <v>514227</v>
       </c>
       <c r="R14" t="n">
-        <v>7023271</v>
+        <v>7023300</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2188,27 +2123,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2226,10 +2161,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121670799</v>
+        <v>121667243</v>
       </c>
       <c r="B15" t="n">
-        <v>79726</v>
+        <v>79733</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2242,39 +2177,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514265</v>
+        <v>514636</v>
       </c>
       <c r="R15" t="n">
-        <v>7023278</v>
+        <v>7023234</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2317,31 +2247,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2358,7 +2263,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121667142</v>
+        <v>121670797</v>
       </c>
       <c r="B16" t="n">
         <v>79698</v>
@@ -2392,16 +2297,21 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514636</v>
+        <v>514262</v>
       </c>
       <c r="R16" t="n">
-        <v>7023234</v>
+        <v>7023275</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2444,6 +2354,31 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2460,10 +2395,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121667649</v>
+        <v>121671169</v>
       </c>
       <c r="B17" t="n">
-        <v>79697</v>
+        <v>79698</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2476,34 +2411,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514709</v>
+        <v>514228</v>
       </c>
       <c r="R17" t="n">
-        <v>7023250</v>
+        <v>7023328</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2562,10 +2497,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121670504</v>
+        <v>121667138</v>
       </c>
       <c r="B18" t="n">
-        <v>79697</v>
+        <v>78616</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2578,34 +2513,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514335</v>
+        <v>514735</v>
       </c>
       <c r="R18" t="n">
-        <v>7023306</v>
+        <v>7023174</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2648,6 +2583,31 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2664,10 +2624,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121671167</v>
+        <v>121670799</v>
       </c>
       <c r="B19" t="n">
-        <v>79697</v>
+        <v>79726</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2676,38 +2636,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514229</v>
+        <v>514265</v>
       </c>
       <c r="R19" t="n">
-        <v>7023329</v>
+        <v>7023278</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2750,6 +2715,31 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2766,7 +2756,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121671149</v>
+        <v>121670772</v>
       </c>
       <c r="B20" t="n">
         <v>79697</v>
@@ -2806,10 +2796,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514237</v>
+        <v>514217</v>
       </c>
       <c r="R20" t="n">
-        <v>7023316</v>
+        <v>7023244</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2868,7 +2858,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121667138</v>
+        <v>121669034</v>
       </c>
       <c r="B21" t="n">
         <v>78616</v>
@@ -2908,10 +2898,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514735</v>
+        <v>514722</v>
       </c>
       <c r="R21" t="n">
-        <v>7023174</v>
+        <v>7023113</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2957,7 +2947,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Våtmark med barrträd</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -2972,12 +2962,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2995,10 +2985,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121670772</v>
+        <v>121666620</v>
       </c>
       <c r="B22" t="n">
-        <v>79697</v>
+        <v>57373</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3011,34 +3001,44 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514217</v>
+        <v>514538</v>
       </c>
       <c r="R22" t="n">
-        <v>7023244</v>
+        <v>7023126</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3081,6 +3081,31 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3097,10 +3122,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121667545</v>
+        <v>121671097</v>
       </c>
       <c r="B23" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3113,34 +3138,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514742</v>
+        <v>514216</v>
       </c>
       <c r="R23" t="n">
-        <v>7023172</v>
+        <v>7023328</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3191,22 +3221,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3224,10 +3254,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121671125</v>
+        <v>121666824</v>
       </c>
       <c r="B24" t="n">
-        <v>79697</v>
+        <v>78616</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3240,39 +3270,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>514222</v>
+        <v>514678</v>
       </c>
       <c r="R24" t="n">
-        <v>7023316</v>
+        <v>7023186</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3323,22 +3348,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3356,10 +3381,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121671097</v>
+        <v>121671072</v>
       </c>
       <c r="B25" t="n">
-        <v>79697</v>
+        <v>57357</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3372,27 +3397,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3401,10 +3426,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>514216</v>
+        <v>514232</v>
       </c>
       <c r="R25" t="n">
-        <v>7023328</v>
+        <v>7023294</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3447,31 +3472,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3488,10 +3488,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121670532</v>
+        <v>121669062</v>
       </c>
       <c r="B26" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3504,36 +3504,27 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3542,10 +3533,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>514314</v>
+        <v>514434</v>
       </c>
       <c r="R26" t="n">
-        <v>7023286</v>
+        <v>7023257</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3588,31 +3579,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3629,10 +3595,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121669062</v>
+        <v>121667163</v>
       </c>
       <c r="B27" t="n">
-        <v>57357</v>
+        <v>79732</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3641,43 +3607,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>514434</v>
+        <v>514636</v>
       </c>
       <c r="R27" t="n">
-        <v>7023257</v>
+        <v>7023234</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3736,10 +3697,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121667143</v>
+        <v>121668931</v>
       </c>
       <c r="B28" t="n">
-        <v>79726</v>
+        <v>78616</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3748,25 +3709,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3776,10 +3737,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>514636</v>
+        <v>514674</v>
       </c>
       <c r="R28" t="n">
-        <v>7023234</v>
+        <v>7023130</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3822,6 +3783,31 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3838,10 +3824,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121669055</v>
+        <v>121670575</v>
       </c>
       <c r="B29" t="n">
-        <v>57357</v>
+        <v>79697</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3854,39 +3840,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>514434</v>
+        <v>514301</v>
       </c>
       <c r="R29" t="n">
-        <v>7023259</v>
+        <v>7023286</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3945,10 +3926,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121669094</v>
+        <v>121670532</v>
       </c>
       <c r="B30" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3961,34 +3942,48 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514711</v>
+        <v>514314</v>
       </c>
       <c r="R30" t="n">
-        <v>7023153</v>
+        <v>7023286</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4034,7 +4029,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Våtmark med barrträd</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4049,12 +4044,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4072,10 +4067,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121666824</v>
+        <v>121670773</v>
       </c>
       <c r="B31" t="n">
-        <v>78616</v>
+        <v>79698</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4088,34 +4083,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>514678</v>
+        <v>514216</v>
       </c>
       <c r="R31" t="n">
-        <v>7023186</v>
+        <v>7023241</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4158,31 +4153,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4199,7 +4169,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121670773</v>
+        <v>121667142</v>
       </c>
       <c r="B32" t="n">
         <v>79698</v>
@@ -4235,14 +4205,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514216</v>
+        <v>514636</v>
       </c>
       <c r="R32" t="n">
-        <v>7023241</v>
+        <v>7023234</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4301,10 +4271,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121671169</v>
+        <v>121668309</v>
       </c>
       <c r="B33" t="n">
-        <v>79698</v>
+        <v>78616</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4317,34 +4287,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>514228</v>
+        <v>514672</v>
       </c>
       <c r="R33" t="n">
-        <v>7023328</v>
+        <v>7023245</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4387,6 +4357,31 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4403,10 +4398,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121670575</v>
+        <v>121669055</v>
       </c>
       <c r="B34" t="n">
-        <v>79697</v>
+        <v>57357</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4419,34 +4414,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514301</v>
+        <v>514434</v>
       </c>
       <c r="R34" t="n">
-        <v>7023286</v>
+        <v>7023259</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>

--- a/artfynd/A 55314-2024 artfynd.xlsx
+++ b/artfynd/A 55314-2024 artfynd.xlsx
@@ -4835,7 +4835,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122208320</v>
+        <v>122208029</v>
       </c>
       <c r="B35" t="n">
         <v>57390</v>
@@ -4876,17 +4876,21 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Lillberget, Klenflon, Häggenås, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514264</v>
+        <v>514232</v>
       </c>
       <c r="R35" t="n">
-        <v>7023177</v>
+        <v>7023309</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4923,7 +4927,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska hackspår av spillkråka i en sälg.</t>
+          <t>Färska rejäla hackspår av spillkråka i basen av en gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4937,32 +4941,32 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Med inslag av gran, sälg och björk.</t>
+          <t>Äldre skog med olikåldriga träd.</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Stem on living tree # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4980,10 +4984,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122208128</v>
+        <v>122207795</v>
       </c>
       <c r="B36" t="n">
-        <v>79726</v>
+        <v>57374</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4996,44 +5000,49 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Sauholmen, Klenflon, Häggenås, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>514240</v>
+        <v>514641</v>
       </c>
       <c r="R36" t="n">
-        <v>7023172</v>
+        <v>7023370</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5067,7 +5076,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ymnig påväxt av lunglav på sälg.</t>
+          <t>Färska hackspår (ringhack), i basen av en gran, som bedöms vara skapade inom 5 år tillbaks. I området kring denna plats finns även födosökspår på stående smala döda granar.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5076,43 +5085,37 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Med inslag av gran, sälg och björk.</t>
+          <t>Grandominerad skog med inslag av tall och björk på frisk-fuktig och fuktig mark.</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL36" t="inlineStr">
-        <is>
-          <t>En skadad knäckt men levande sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En skadad knäckt men levande sälg.</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5130,10 +5133,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122208210</v>
+        <v>122208320</v>
       </c>
       <c r="B37" t="n">
-        <v>79726</v>
+        <v>57390</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5146,28 +5149,29 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5215,13 +5219,17 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska hackspår av spillkråka i en sälg.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5247,12 +5255,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Salix caprea</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5391,10 +5399,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122208029</v>
+        <v>122191658</v>
       </c>
       <c r="B39" t="n">
-        <v>57390</v>
+        <v>78645</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5407,49 +5415,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lillberget, Klenflon, Häggenås, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>514232</v>
+        <v>514512</v>
       </c>
       <c r="R39" t="n">
-        <v>7023309</v>
+        <v>7023275</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5481,11 +5477,6 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Färska rejäla hackspår av spillkråka i basen av en gran.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5497,12 +5488,7 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>Äldre skog med olikåldriga träd.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
@@ -5517,12 +5503,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5540,10 +5526,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122191658</v>
+        <v>122208128</v>
       </c>
       <c r="B40" t="n">
-        <v>78645</v>
+        <v>79726</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5556,34 +5542,41 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>514512</v>
+        <v>514240</v>
       </c>
       <c r="R40" t="n">
-        <v>7023275</v>
+        <v>7023172</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5618,38 +5611,54 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ymnig påväxt av lunglav på sälg.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Med inslag av gran, sälg och björk.</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL40" t="inlineStr">
+        <is>
+          <t>En skadad knäckt men levande sälg.</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En skadad knäckt men levande sälg.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5667,10 +5676,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122193443</v>
+        <v>122208210</v>
       </c>
       <c r="B41" t="n">
-        <v>90797</v>
+        <v>79726</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5683,51 +5692,44 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>514671</v>
+        <v>514264</v>
       </c>
       <c r="R41" t="n">
-        <v>7023306</v>
+        <v>7023177</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5765,32 +5767,38 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Med inslag av gran, sälg och björk.</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5935,10 +5943,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122207795</v>
+        <v>122193443</v>
       </c>
       <c r="B43" t="n">
-        <v>57374</v>
+        <v>90797</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5951,49 +5959,51 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sauholmen, Klenflon, Häggenås, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>514641</v>
+        <v>514671</v>
       </c>
       <c r="R43" t="n">
-        <v>7023370</v>
+        <v>7023306</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6025,11 +6035,6 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Färska hackspår (ringhack), i basen av en gran, som bedöms vara skapade inom 5 år tillbaks. I området kring denna plats finns även födosökspår på stående smala döda granar.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -6041,12 +6046,7 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall och björk på frisk-fuktig och fuktig mark.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -6220,10 +6220,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122223793</v>
+        <v>122223410</v>
       </c>
       <c r="B45" t="n">
-        <v>79726</v>
+        <v>57390</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6236,41 +6236,46 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sauholmen, Jmt</t>
+          <t>Sauholmen, Klenflon, Häggenås, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>514631</v>
+        <v>514617</v>
       </c>
       <c r="R45" t="n">
-        <v>7023229</v>
+        <v>7023224</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -6307,7 +6312,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ett par "knippen" med lunglav på en grovbarkad sälg.</t>
+          <t>Relativt nyligen använt bohål på ca 4 meters höjd i en delvis skadad och hålig asp.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6316,7 +6321,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6332,27 +6336,27 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AL45" t="inlineStr">
         <is>
-          <t>En något smalare men grovbarkad sälg.</t>
+          <t>En asp med uppskattningvis minst 30 cm i brösthöjdsdiameter. I trädets stam finns även fler håligheter och en uthackad skada i trädets stambas.</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea # En något smalare men grovbarkad sälg.</t>
+          <t>Stem on living tree # Populus tremula # En asp med uppskattningvis minst 30 cm i brösthöjdsdiameter. I trädets stam finns även fler håligheter och en uthackad skada i trädets stambas.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6370,10 +6374,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122194394</v>
+        <v>122193783</v>
       </c>
       <c r="B46" t="n">
-        <v>79727</v>
+        <v>79726</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6386,21 +6390,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6413,14 +6417,14 @@
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>514600</v>
+        <v>514670</v>
       </c>
       <c r="R46" t="n">
-        <v>7023243</v>
+        <v>7023247</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6492,7 +6496,7 @@
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>En smal skadad knäckt sälg.</t>
+          <t>En knäckt smal relativt grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
@@ -6502,7 +6506,7 @@
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Grov bark. # Salix caprea # En smal skadad knäckt sälg.</t>
+          <t>Bark of dead wood # Salix caprea # En knäckt smal relativt grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6520,10 +6524,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122223410</v>
+        <v>122194568</v>
       </c>
       <c r="B47" t="n">
-        <v>57390</v>
+        <v>57374</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6536,16 +6540,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -6558,7 +6562,7 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -6568,17 +6572,17 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sauholmen, Klenflon, Häggenås, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>514617</v>
+        <v>514580</v>
       </c>
       <c r="R47" t="n">
-        <v>7023224</v>
+        <v>7023243</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6612,7 +6616,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Relativt nyligen använt bohål på ca 4 meters höjd i en delvis skadad och hålig asp.</t>
+          <t>Äldre ringhack på basen av en gran.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6636,17 +6640,12 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AL47" t="inlineStr">
-        <is>
-          <t>En asp med uppskattningvis minst 30 cm i brösthöjdsdiameter. I trädets stam finns även fler håligheter och en uthackad skada i trädets stambas.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
@@ -6656,7 +6655,7 @@
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Stem on living tree # Populus tremula # En asp med uppskattningvis minst 30 cm i brösthöjdsdiameter. I trädets stam finns även fler håligheter och en uthackad skada i trädets stambas.</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6674,10 +6673,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122226624</v>
+        <v>122194394</v>
       </c>
       <c r="B48" t="n">
-        <v>78645</v>
+        <v>79727</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6690,40 +6689,44 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>514188</v>
+        <v>514600</v>
       </c>
       <c r="R48" t="n">
-        <v>7023245</v>
+        <v>7023243</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6757,7 +6760,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Garnlav på flera granar.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6777,27 +6780,32 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Äldre barrskog med en mosaik av talldominerade och grandominerade partier på frisk till fuktig mark.</t>
+          <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>En smal skadad knäckt sälg.</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Grov bark. # Salix caprea # En smal skadad knäckt sälg.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6815,10 +6823,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122194568</v>
+        <v>122223793</v>
       </c>
       <c r="B49" t="n">
-        <v>57374</v>
+        <v>79726</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6831,49 +6839,44 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514580</v>
+        <v>514631</v>
       </c>
       <c r="R49" t="n">
-        <v>7023243</v>
+        <v>7023229</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6907,7 +6910,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Äldre ringhack på basen av en gran.</t>
+          <t>Ett par "knippen" med lunglav på en grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6916,6 +6919,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6931,22 +6935,27 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL49" t="inlineStr">
+        <is>
+          <t>En något smalare men grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En något smalare men grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6964,7 +6973,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122226449</v>
+        <v>122226624</v>
       </c>
       <c r="B50" t="n">
         <v>78645</v>
@@ -7007,10 +7016,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514425</v>
+        <v>514188</v>
       </c>
       <c r="R50" t="n">
-        <v>7023228</v>
+        <v>7023245</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -7047,7 +7056,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flera granar.</t>
+          <t>Garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7062,12 +7071,12 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk till fuktig mark. Här finns både stående och liggande död ved. Kolade stubbar indikerar tidigare brandpåverkan.</t>
+          <t>Äldre barrskog med en mosaik av talldominerade och grandominerade partier på frisk till fuktig mark.</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -7105,10 +7114,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122193783</v>
+        <v>122226449</v>
       </c>
       <c r="B51" t="n">
-        <v>79726</v>
+        <v>78645</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7121,44 +7130,40 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>514670</v>
+        <v>514425</v>
       </c>
       <c r="R51" t="n">
-        <v>7023247</v>
+        <v>7023228</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7192,7 +7197,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>Långväxt garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7207,37 +7212,32 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk till fuktig mark. Här finns både stående och liggande död ved. Kolade stubbar indikerar tidigare brandpåverkan.</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL51" t="inlineStr">
-        <is>
-          <t>En knäckt smal relativt grovbarkad sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En knäckt smal relativt grovbarkad sälg.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>

--- a/artfynd/A 55314-2024 artfynd.xlsx
+++ b/artfynd/A 55314-2024 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>121667141</v>
       </c>
       <c r="B3" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>121667143</v>
       </c>
       <c r="B11" t="n">
-        <v>79755</v>
+        <v>79756</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
         <v>121667163</v>
       </c>
       <c r="B29" t="n">
-        <v>79761</v>
+        <v>79762</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>121667243</v>
       </c>
       <c r="B32" t="n">
-        <v>79762</v>
+        <v>79763</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>121667142</v>
       </c>
       <c r="B34" t="n">
-        <v>79727</v>
+        <v>79728</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4835,10 +4835,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122208029</v>
+        <v>122192869</v>
       </c>
       <c r="B35" t="n">
-        <v>57390</v>
+        <v>78646</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4851,49 +4851,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lillberget, Klenflon, Häggenås, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514232</v>
+        <v>514655</v>
       </c>
       <c r="R35" t="n">
-        <v>7023309</v>
+        <v>7023373</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4925,11 +4913,6 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Färska rejäla hackspår av spillkråka i basen av en gran.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4941,12 +4924,7 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Äldre skog med olikåldriga träd.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -4961,12 +4939,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4984,10 +4962,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122207795</v>
+        <v>122191658</v>
       </c>
       <c r="B36" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5000,49 +4978,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sauholmen, Klenflon, Häggenås, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>514641</v>
+        <v>514512</v>
       </c>
       <c r="R36" t="n">
-        <v>7023370</v>
+        <v>7023275</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5074,11 +5040,6 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Färska hackspår (ringhack), i basen av en gran, som bedöms vara skapade inom 5 år tillbaks. I området kring denna plats finns även födosökspår på stående smala döda granar.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -5090,12 +5051,7 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall och björk på frisk-fuktig och fuktig mark.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -5110,12 +5066,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5278,10 +5234,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122193236</v>
+        <v>122208029</v>
       </c>
       <c r="B38" t="n">
-        <v>57527</v>
+        <v>57390</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5294,31 +5250,29 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -5328,17 +5282,17 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Klenflon, Häggenås, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>514622</v>
+        <v>514232</v>
       </c>
       <c r="R38" t="n">
-        <v>7023310</v>
+        <v>7023309</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5370,6 +5324,11 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska rejäla hackspår av spillkråka i basen av en gran.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5381,7 +5340,32 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Äldre skog med olikåldriga träd.</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5399,10 +5383,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122191658</v>
+        <v>122193236</v>
       </c>
       <c r="B39" t="n">
-        <v>78645</v>
+        <v>57527</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5415,34 +5399,48 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>514512</v>
+        <v>514622</v>
       </c>
       <c r="R39" t="n">
-        <v>7023275</v>
+        <v>7023310</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5489,26 +5487,6 @@
       <c r="AH39" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5526,10 +5504,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122208128</v>
+        <v>122208210</v>
       </c>
       <c r="B40" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5573,13 +5551,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>514240</v>
+        <v>514264</v>
       </c>
       <c r="R40" t="n">
-        <v>7023172</v>
+        <v>7023177</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5609,11 +5587,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-01-18</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ymnig påväxt av lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5646,11 +5619,6 @@
           <t>Salix caprea</t>
         </is>
       </c>
-      <c r="AL40" t="inlineStr">
-        <is>
-          <t>En skadad knäckt men levande sälg.</t>
-        </is>
-      </c>
       <c r="AM40" t="inlineStr">
         <is>
           <t>Bark på levande träd</t>
@@ -5658,7 +5626,7 @@
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En skadad knäckt men levande sälg.</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5676,10 +5644,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122208210</v>
+        <v>122208128</v>
       </c>
       <c r="B41" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5723,13 +5691,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>514264</v>
+        <v>514240</v>
       </c>
       <c r="R41" t="n">
-        <v>7023177</v>
+        <v>7023172</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5759,6 +5727,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-01-18</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ymnig påväxt av lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5791,6 +5764,11 @@
           <t>Salix caprea</t>
         </is>
       </c>
+      <c r="AL41" t="inlineStr">
+        <is>
+          <t>En skadad knäckt men levande sälg.</t>
+        </is>
+      </c>
       <c r="AM41" t="inlineStr">
         <is>
           <t>Bark på levande träd</t>
@@ -5798,7 +5776,7 @@
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea # En skadad knäckt men levande sälg.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5816,10 +5794,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122192869</v>
+        <v>122193443</v>
       </c>
       <c r="B42" t="n">
-        <v>78645</v>
+        <v>90807</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5832,34 +5810,48 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>514655</v>
+        <v>514671</v>
       </c>
       <c r="R42" t="n">
-        <v>7023373</v>
+        <v>7023306</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5920,12 +5912,12 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5943,10 +5935,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122193443</v>
+        <v>122207795</v>
       </c>
       <c r="B43" t="n">
-        <v>90797</v>
+        <v>57374</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5959,51 +5951,49 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Sauholmen, Klenflon, Häggenås, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>514671</v>
+        <v>514641</v>
       </c>
       <c r="R43" t="n">
-        <v>7023306</v>
+        <v>7023370</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6035,6 +6025,11 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färska hackspår (ringhack), i basen av en gran, som bedöms vara skapade inom 5 år tillbaks. I området kring denna plats finns även födosökspår på stående smala döda granar.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -6046,7 +6041,12 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall och björk på frisk-fuktig och fuktig mark.</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -6084,10 +6084,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122194308</v>
+        <v>122194394</v>
       </c>
       <c r="B44" t="n">
-        <v>78645</v>
+        <v>79728</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6100,26 +6100,30 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6127,10 +6131,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>514604</v>
+        <v>514600</v>
       </c>
       <c r="R44" t="n">
-        <v>7023237</v>
+        <v>7023243</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6165,6 +6169,11 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -6187,22 +6196,27 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL44" t="inlineStr">
+        <is>
+          <t>En smal skadad knäckt sälg.</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Grov bark. # Salix caprea # En smal skadad knäckt sälg.</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6220,10 +6234,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122223410</v>
+        <v>122194568</v>
       </c>
       <c r="B45" t="n">
-        <v>57390</v>
+        <v>57374</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6236,16 +6250,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -6258,7 +6272,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -6268,17 +6282,17 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sauholmen, Klenflon, Häggenås, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>514617</v>
+        <v>514580</v>
       </c>
       <c r="R45" t="n">
-        <v>7023224</v>
+        <v>7023243</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6312,7 +6326,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Relativt nyligen använt bohål på ca 4 meters höjd i en delvis skadad och hålig asp.</t>
+          <t>Äldre ringhack på basen av en gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6336,17 +6350,12 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AL45" t="inlineStr">
-        <is>
-          <t>En asp med uppskattningvis minst 30 cm i brösthöjdsdiameter. I trädets stam finns även fler håligheter och en uthackad skada i trädets stambas.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
@@ -6356,7 +6365,7 @@
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Stem on living tree # Populus tremula # En asp med uppskattningvis minst 30 cm i brösthöjdsdiameter. I trädets stam finns även fler håligheter och en uthackad skada i trädets stambas.</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6374,10 +6383,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122193783</v>
+        <v>122223793</v>
       </c>
       <c r="B46" t="n">
-        <v>79726</v>
+        <v>79727</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6417,17 +6426,17 @@
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>514670</v>
+        <v>514631</v>
       </c>
       <c r="R46" t="n">
-        <v>7023247</v>
+        <v>7023229</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6461,7 +6470,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>Ett par "knippen" med lunglav på en grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6496,17 +6505,17 @@
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>En knäckt smal relativt grovbarkad sälg.</t>
+          <t>En något smalare men grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En knäckt smal relativt grovbarkad sälg.</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En något smalare men grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6524,10 +6533,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122194568</v>
+        <v>122193783</v>
       </c>
       <c r="B47" t="n">
-        <v>57374</v>
+        <v>79727</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6540,46 +6549,41 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>514580</v>
+        <v>514670</v>
       </c>
       <c r="R47" t="n">
-        <v>7023243</v>
+        <v>7023247</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6616,7 +6620,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Äldre ringhack på basen av en gran.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6625,6 +6629,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6640,22 +6645,27 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL47" t="inlineStr">
+        <is>
+          <t>En knäckt smal relativt grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea # En knäckt smal relativt grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6673,10 +6683,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122194394</v>
+        <v>122194308</v>
       </c>
       <c r="B48" t="n">
-        <v>79727</v>
+        <v>78646</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6689,30 +6699,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6720,10 +6726,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>514600</v>
+        <v>514604</v>
       </c>
       <c r="R48" t="n">
-        <v>7023243</v>
+        <v>7023237</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6758,11 +6764,6 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6785,27 +6786,22 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL48" t="inlineStr">
-        <is>
-          <t>En smal skadad knäckt sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Grov bark. # Salix caprea # En smal skadad knäckt sälg.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6823,10 +6819,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122223793</v>
+        <v>122223410</v>
       </c>
       <c r="B49" t="n">
-        <v>79726</v>
+        <v>57390</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6839,41 +6835,46 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sauholmen, Jmt</t>
+          <t>Sauholmen, Klenflon, Häggenås, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514631</v>
+        <v>514617</v>
       </c>
       <c r="R49" t="n">
-        <v>7023229</v>
+        <v>7023224</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6910,7 +6911,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ett par "knippen" med lunglav på en grovbarkad sälg.</t>
+          <t>Relativt nyligen använt bohål på ca 4 meters höjd i en delvis skadad och hålig asp.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6919,7 +6920,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6935,27 +6935,27 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AL49" t="inlineStr">
         <is>
-          <t>En något smalare men grovbarkad sälg.</t>
+          <t>En asp med uppskattningvis minst 30 cm i brösthöjdsdiameter. I trädets stam finns även fler håligheter och en uthackad skada i trädets stambas.</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea # En något smalare men grovbarkad sälg.</t>
+          <t>Stem on living tree # Populus tremula # En asp med uppskattningvis minst 30 cm i brösthöjdsdiameter. I trädets stam finns även fler håligheter och en uthackad skada i trädets stambas.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6973,10 +6973,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122226624</v>
+        <v>122226449</v>
       </c>
       <c r="B50" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7016,10 +7016,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514188</v>
+        <v>514425</v>
       </c>
       <c r="R50" t="n">
-        <v>7023245</v>
+        <v>7023228</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Garnlav på flera granar.</t>
+          <t>Långväxt garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7071,12 +7071,12 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Äldre barrskog med en mosaik av talldominerade och grandominerade partier på frisk till fuktig mark.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk till fuktig mark. Här finns både stående och liggande död ved. Kolade stubbar indikerar tidigare brandpåverkan.</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -7114,10 +7114,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122226449</v>
+        <v>122226624</v>
       </c>
       <c r="B51" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7157,10 +7157,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>514425</v>
+        <v>514188</v>
       </c>
       <c r="R51" t="n">
-        <v>7023228</v>
+        <v>7023245</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -7197,7 +7197,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flera granar.</t>
+          <t>Garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk till fuktig mark. Här finns både stående och liggande död ved. Kolade stubbar indikerar tidigare brandpåverkan.</t>
+          <t>Äldre barrskog med en mosaik av talldominerade och grandominerade partier på frisk till fuktig mark.</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">

--- a/artfynd/A 55314-2024 artfynd.xlsx
+++ b/artfynd/A 55314-2024 artfynd.xlsx
@@ -4835,10 +4835,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122192869</v>
+        <v>122208029</v>
       </c>
       <c r="B35" t="n">
-        <v>78646</v>
+        <v>57390</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4851,37 +4851,49 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Klenflon, Häggenås, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514655</v>
+        <v>514232</v>
       </c>
       <c r="R35" t="n">
-        <v>7023373</v>
+        <v>7023309</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4913,6 +4925,11 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska rejäla hackspår av spillkråka i basen av en gran.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4924,7 +4941,12 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Äldre skog med olikåldriga träd.</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -4939,12 +4961,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4962,10 +4984,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122191658</v>
+        <v>122193236</v>
       </c>
       <c r="B36" t="n">
-        <v>78646</v>
+        <v>57527</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4978,34 +5000,48 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>514512</v>
+        <v>514622</v>
       </c>
       <c r="R36" t="n">
-        <v>7023275</v>
+        <v>7023310</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5052,26 +5088,6 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5089,10 +5105,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122208320</v>
+        <v>122208128</v>
       </c>
       <c r="B37" t="n">
-        <v>57390</v>
+        <v>79727</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5105,29 +5121,28 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5137,13 +5152,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>514264</v>
+        <v>514240</v>
       </c>
       <c r="R37" t="n">
-        <v>7023177</v>
+        <v>7023172</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5177,7 +5192,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Färska hackspår av spillkråka i en sälg.</t>
+          <t>Ymnig påväxt av lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5186,6 +5201,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5209,14 +5225,19 @@
           <t>Salix caprea</t>
         </is>
       </c>
+      <c r="AL37" t="inlineStr">
+        <is>
+          <t>En skadad knäckt men levande sälg.</t>
+        </is>
+      </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea # En skadad knäckt men levande sälg.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5234,10 +5255,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122208029</v>
+        <v>122192869</v>
       </c>
       <c r="B38" t="n">
-        <v>57390</v>
+        <v>78646</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5250,49 +5271,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lillberget, Klenflon, Häggenås, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>514232</v>
+        <v>514655</v>
       </c>
       <c r="R38" t="n">
-        <v>7023309</v>
+        <v>7023373</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5324,11 +5333,6 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska rejäla hackspår av spillkråka i basen av en gran.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5340,12 +5344,7 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Äldre skog med olikåldriga träd.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -5360,12 +5359,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5383,10 +5382,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122193236</v>
+        <v>122193443</v>
       </c>
       <c r="B39" t="n">
-        <v>57527</v>
+        <v>90807</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5399,21 +5398,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5421,14 +5420,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5437,10 +5436,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>514622</v>
+        <v>514671</v>
       </c>
       <c r="R39" t="n">
-        <v>7023310</v>
+        <v>7023306</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5487,6 +5486,26 @@
       <c r="AH39" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5504,10 +5523,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122208210</v>
+        <v>122208320</v>
       </c>
       <c r="B40" t="n">
-        <v>79727</v>
+        <v>57390</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5520,28 +5539,29 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -5589,13 +5609,17 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska hackspår av spillkråka i en sälg.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5621,12 +5645,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5644,10 +5668,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122208128</v>
+        <v>122207795</v>
       </c>
       <c r="B41" t="n">
-        <v>79727</v>
+        <v>57374</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5660,44 +5684,49 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Sauholmen, Klenflon, Häggenås, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>514240</v>
+        <v>514641</v>
       </c>
       <c r="R41" t="n">
-        <v>7023172</v>
+        <v>7023370</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5731,7 +5760,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ymnig påväxt av lunglav på sälg.</t>
+          <t>Färska hackspår (ringhack), i basen av en gran, som bedöms vara skapade inom 5 år tillbaks. I området kring denna plats finns även födosökspår på stående smala döda granar.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5740,43 +5769,37 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Med inslag av gran, sälg och björk.</t>
+          <t>Grandominerad skog med inslag av tall och björk på frisk-fuktig och fuktig mark.</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL41" t="inlineStr">
-        <is>
-          <t>En skadad knäckt men levande sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En skadad knäckt men levande sälg.</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5794,10 +5817,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122193443</v>
+        <v>122208210</v>
       </c>
       <c r="B42" t="n">
-        <v>90807</v>
+        <v>79727</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5810,51 +5833,44 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>514671</v>
+        <v>514264</v>
       </c>
       <c r="R42" t="n">
-        <v>7023306</v>
+        <v>7023177</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5892,32 +5908,38 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Med inslag av gran, sälg och björk.</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5935,10 +5957,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122207795</v>
+        <v>122191658</v>
       </c>
       <c r="B43" t="n">
-        <v>57374</v>
+        <v>78646</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5951,49 +5973,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sauholmen, Klenflon, Häggenås, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>514641</v>
+        <v>514512</v>
       </c>
       <c r="R43" t="n">
-        <v>7023370</v>
+        <v>7023275</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6025,11 +6035,6 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Färska hackspår (ringhack), i basen av en gran, som bedöms vara skapade inom 5 år tillbaks. I området kring denna plats finns även födosökspår på stående smala döda granar.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -6041,12 +6046,7 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall och björk på frisk-fuktig och fuktig mark.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6084,10 +6084,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122194394</v>
+        <v>122194568</v>
       </c>
       <c r="B44" t="n">
-        <v>79728</v>
+        <v>57374</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6100,38 +6100,43 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>514600</v>
+        <v>514580</v>
       </c>
       <c r="R44" t="n">
         <v>7023243</v>
@@ -6171,7 +6176,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>Äldre ringhack på basen av en gran.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6180,7 +6185,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6196,27 +6200,22 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL44" t="inlineStr">
-        <is>
-          <t>En smal skadad knäckt sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Grov bark. # Salix caprea # En smal skadad knäckt sälg.</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6234,10 +6233,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122194568</v>
+        <v>122223410</v>
       </c>
       <c r="B45" t="n">
-        <v>57374</v>
+        <v>57390</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6250,16 +6249,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -6272,7 +6271,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -6282,17 +6281,17 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Klenflon, Häggenås, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>514580</v>
+        <v>514617</v>
       </c>
       <c r="R45" t="n">
-        <v>7023243</v>
+        <v>7023224</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6326,7 +6325,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Äldre ringhack på basen av en gran.</t>
+          <t>Relativt nyligen använt bohål på ca 4 meters höjd i en delvis skadad och hålig asp.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6350,12 +6349,17 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AL45" t="inlineStr">
+        <is>
+          <t>En asp med uppskattningvis minst 30 cm i brösthöjdsdiameter. I trädets stam finns även fler håligheter och en uthackad skada i trädets stambas.</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
@@ -6365,7 +6369,7 @@
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Populus tremula # En asp med uppskattningvis minst 30 cm i brösthöjdsdiameter. I trädets stam finns även fler håligheter och en uthackad skada i trädets stambas.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6383,10 +6387,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122223793</v>
+        <v>122194308</v>
       </c>
       <c r="B46" t="n">
-        <v>79727</v>
+        <v>78646</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6399,44 +6403,40 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sauholmen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>514631</v>
+        <v>514604</v>
       </c>
       <c r="R46" t="n">
-        <v>7023229</v>
+        <v>7023237</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6466,11 +6466,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-01-18</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ett par "knippen" med lunglav på en grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6495,27 +6490,22 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL46" t="inlineStr">
-        <is>
-          <t>En något smalare men grovbarkad sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea # En något smalare men grovbarkad sälg.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6683,10 +6673,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122194308</v>
+        <v>122194394</v>
       </c>
       <c r="B48" t="n">
-        <v>78646</v>
+        <v>79728</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6699,26 +6689,30 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6726,10 +6720,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>514604</v>
+        <v>514600</v>
       </c>
       <c r="R48" t="n">
-        <v>7023237</v>
+        <v>7023243</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6764,6 +6758,11 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6786,22 +6785,27 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>En smal skadad knäckt sälg.</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Grov bark. # Salix caprea # En smal skadad knäckt sälg.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6819,10 +6823,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122223410</v>
+        <v>122226624</v>
       </c>
       <c r="B49" t="n">
-        <v>57390</v>
+        <v>78646</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6835,46 +6839,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sauholmen, Klenflon, Häggenås, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514617</v>
+        <v>514188</v>
       </c>
       <c r="R49" t="n">
-        <v>7023224</v>
+        <v>7023245</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6911,7 +6906,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Relativt nyligen använt bohål på ca 4 meters höjd i en delvis skadad och hålig asp.</t>
+          <t>Garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6920,6 +6915,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6930,32 +6926,27 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
+          <t>Äldre barrskog med en mosaik av talldominerade och grandominerade partier på frisk till fuktig mark.</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AL49" t="inlineStr">
-        <is>
-          <t>En asp med uppskattningvis minst 30 cm i brösthöjdsdiameter. I trädets stam finns även fler håligheter och en uthackad skada i trädets stambas.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Stem on living tree # Populus tremula # En asp med uppskattningvis minst 30 cm i brösthöjdsdiameter. I trädets stam finns även fler håligheter och en uthackad skada i trädets stambas.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7114,10 +7105,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122226624</v>
+        <v>122223793</v>
       </c>
       <c r="B51" t="n">
-        <v>78646</v>
+        <v>79727</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7130,37 +7121,41 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>514188</v>
+        <v>514631</v>
       </c>
       <c r="R51" t="n">
-        <v>7023245</v>
+        <v>7023229</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -7197,7 +7192,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Garnlav på flera granar.</t>
+          <t>Ett par "knippen" med lunglav på en grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7217,27 +7212,32 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Äldre barrskog med en mosaik av talldominerade och grandominerade partier på frisk till fuktig mark.</t>
+          <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL51" t="inlineStr">
+        <is>
+          <t>En något smalare men grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En något smalare men grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>

--- a/artfynd/A 55314-2024 artfynd.xlsx
+++ b/artfynd/A 55314-2024 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>121667141</v>
       </c>
       <c r="B3" t="n">
-        <v>79727</v>
+        <v>79732</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>121669062</v>
       </c>
       <c r="B5" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>121667143</v>
       </c>
       <c r="B11" t="n">
-        <v>79756</v>
+        <v>79761</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         <v>121669887</v>
       </c>
       <c r="B22" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
         <v>121667163</v>
       </c>
       <c r="B29" t="n">
-        <v>79762</v>
+        <v>79767</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>121669055</v>
       </c>
       <c r="B30" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>121667243</v>
       </c>
       <c r="B32" t="n">
-        <v>79763</v>
+        <v>79768</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>121667142</v>
       </c>
       <c r="B34" t="n">
-        <v>79728</v>
+        <v>79733</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4835,10 +4835,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122208029</v>
+        <v>122191658</v>
       </c>
       <c r="B35" t="n">
-        <v>57390</v>
+        <v>78651</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4851,49 +4851,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lillberget, Klenflon, Häggenås, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514232</v>
+        <v>514512</v>
       </c>
       <c r="R35" t="n">
-        <v>7023309</v>
+        <v>7023275</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4925,11 +4913,6 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Färska rejäla hackspår av spillkråka i basen av en gran.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4941,12 +4924,7 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Äldre skog med olikåldriga träd.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -4961,12 +4939,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4984,10 +4962,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122193236</v>
+        <v>122208029</v>
       </c>
       <c r="B36" t="n">
-        <v>57527</v>
+        <v>57395</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5000,31 +4978,29 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -5034,17 +5010,17 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Klenflon, Häggenås, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>514622</v>
+        <v>514232</v>
       </c>
       <c r="R36" t="n">
-        <v>7023310</v>
+        <v>7023309</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5076,6 +5052,11 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska rejäla hackspår av spillkråka i basen av en gran.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -5087,7 +5068,32 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Äldre skog med olikåldriga träd.</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5105,10 +5111,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122208128</v>
+        <v>122193443</v>
       </c>
       <c r="B37" t="n">
-        <v>79727</v>
+        <v>90819</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5121,41 +5127,48 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>514240</v>
+        <v>514671</v>
       </c>
       <c r="R37" t="n">
-        <v>7023172</v>
+        <v>7023306</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5190,54 +5203,38 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ymnig påväxt av lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>Med inslag av gran, sälg och björk.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL37" t="inlineStr">
-        <is>
-          <t>En skadad knäckt men levande sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En skadad knäckt men levande sälg.</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5255,10 +5252,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122192869</v>
+        <v>122208320</v>
       </c>
       <c r="B38" t="n">
-        <v>78646</v>
+        <v>57395</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5271,37 +5268,45 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>514655</v>
+        <v>514264</v>
       </c>
       <c r="R38" t="n">
-        <v>7023373</v>
+        <v>7023177</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5333,6 +5338,11 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska hackspår av spillkråka i en sälg.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5344,27 +5354,32 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Med inslag av gran, sälg och björk.</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5382,10 +5397,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122193443</v>
+        <v>122208128</v>
       </c>
       <c r="B39" t="n">
-        <v>90807</v>
+        <v>79732</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5398,48 +5413,41 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>514671</v>
+        <v>514240</v>
       </c>
       <c r="R39" t="n">
-        <v>7023306</v>
+        <v>7023172</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5474,38 +5482,54 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ymnig påväxt av lunglav på sälg.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Med inslag av gran, sälg och björk.</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL39" t="inlineStr">
+        <is>
+          <t>En skadad knäckt men levande sälg.</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En skadad knäckt men levande sälg.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5523,10 +5547,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122208320</v>
+        <v>122208210</v>
       </c>
       <c r="B40" t="n">
-        <v>57390</v>
+        <v>79732</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5539,29 +5563,28 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -5609,17 +5632,13 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färska hackspår av spillkråka i en sälg.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5645,12 +5664,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Stem on living tree # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5668,10 +5687,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122207795</v>
+        <v>122193236</v>
       </c>
       <c r="B41" t="n">
-        <v>57374</v>
+        <v>57532</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5684,29 +5703,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -5716,17 +5737,17 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sauholmen, Klenflon, Häggenås, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>514641</v>
+        <v>514622</v>
       </c>
       <c r="R41" t="n">
-        <v>7023370</v>
+        <v>7023310</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5758,11 +5779,6 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Färska hackspår (ringhack), i basen av en gran, som bedöms vara skapade inom 5 år tillbaks. I området kring denna plats finns även födosökspår på stående smala döda granar.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5774,32 +5790,7 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall och björk på frisk-fuktig och fuktig mark.</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5817,10 +5808,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122208210</v>
+        <v>122192869</v>
       </c>
       <c r="B42" t="n">
-        <v>79727</v>
+        <v>78651</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5833,44 +5824,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>514264</v>
+        <v>514655</v>
       </c>
       <c r="R42" t="n">
-        <v>7023177</v>
+        <v>7023373</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5908,38 +5892,32 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Med inslag av gran, sälg och björk.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5957,10 +5935,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122191658</v>
+        <v>122207795</v>
       </c>
       <c r="B43" t="n">
-        <v>78646</v>
+        <v>57379</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5973,37 +5951,49 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Klenflon, Häggenås, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>514512</v>
+        <v>514641</v>
       </c>
       <c r="R43" t="n">
-        <v>7023275</v>
+        <v>7023370</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6035,6 +6025,11 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färska hackspår (ringhack), i basen av en gran, som bedöms vara skapade inom 5 år tillbaks. I området kring denna plats finns även födosökspår på stående smala döda granar.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -6046,7 +6041,12 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall och björk på frisk-fuktig och fuktig mark.</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6084,10 +6084,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122194568</v>
+        <v>122223793</v>
       </c>
       <c r="B44" t="n">
-        <v>57374</v>
+        <v>79732</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6100,49 +6100,44 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>514580</v>
+        <v>514631</v>
       </c>
       <c r="R44" t="n">
-        <v>7023243</v>
+        <v>7023229</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6176,7 +6171,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Äldre ringhack på basen av en gran.</t>
+          <t>Ett par "knippen" med lunglav på en grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6185,6 +6180,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6200,22 +6196,27 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL44" t="inlineStr">
+        <is>
+          <t>En något smalare men grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En något smalare men grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6233,10 +6234,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122223410</v>
+        <v>122194568</v>
       </c>
       <c r="B45" t="n">
-        <v>57390</v>
+        <v>57379</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6249,16 +6250,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -6271,7 +6272,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -6281,17 +6282,17 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sauholmen, Klenflon, Häggenås, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>514617</v>
+        <v>514580</v>
       </c>
       <c r="R45" t="n">
-        <v>7023224</v>
+        <v>7023243</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6325,7 +6326,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Relativt nyligen använt bohål på ca 4 meters höjd i en delvis skadad och hålig asp.</t>
+          <t>Äldre ringhack på basen av en gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6349,17 +6350,12 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AL45" t="inlineStr">
-        <is>
-          <t>En asp med uppskattningvis minst 30 cm i brösthöjdsdiameter. I trädets stam finns även fler håligheter och en uthackad skada i trädets stambas.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
@@ -6369,7 +6365,7 @@
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Stem on living tree # Populus tremula # En asp med uppskattningvis minst 30 cm i brösthöjdsdiameter. I trädets stam finns även fler håligheter och en uthackad skada i trädets stambas.</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6387,10 +6383,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122194308</v>
+        <v>122223410</v>
       </c>
       <c r="B46" t="n">
-        <v>78646</v>
+        <v>57395</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6403,40 +6399,49 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Klenflon, Häggenås, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>514604</v>
+        <v>514617</v>
       </c>
       <c r="R46" t="n">
-        <v>7023237</v>
+        <v>7023224</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6468,13 +6473,17 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Relativt nyligen använt bohål på ca 4 meters höjd i en delvis skadad och hålig asp.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6490,22 +6499,27 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AL46" t="inlineStr">
+        <is>
+          <t>En asp med uppskattningvis minst 30 cm i brösthöjdsdiameter. I trädets stam finns även fler håligheter och en uthackad skada i trädets stambas.</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Populus tremula # En asp med uppskattningvis minst 30 cm i brösthöjdsdiameter. I trädets stam finns även fler håligheter och en uthackad skada i trädets stambas.</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6523,10 +6537,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122193783</v>
+        <v>122194308</v>
       </c>
       <c r="B47" t="n">
-        <v>79727</v>
+        <v>78651</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6539,41 +6553,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>514670</v>
+        <v>514604</v>
       </c>
       <c r="R47" t="n">
-        <v>7023247</v>
+        <v>7023237</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6608,11 +6618,6 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6635,27 +6640,22 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL47" t="inlineStr">
-        <is>
-          <t>En knäckt smal relativt grovbarkad sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En knäckt smal relativt grovbarkad sälg.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6673,10 +6673,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122194394</v>
+        <v>122226449</v>
       </c>
       <c r="B48" t="n">
-        <v>79728</v>
+        <v>78651</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6689,44 +6689,40 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>514600</v>
+        <v>514425</v>
       </c>
       <c r="R48" t="n">
-        <v>7023243</v>
+        <v>7023228</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6760,7 +6756,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>Långväxt garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6775,37 +6771,32 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk till fuktig mark. Här finns både stående och liggande död ved. Kolade stubbar indikerar tidigare brandpåverkan.</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL48" t="inlineStr">
-        <is>
-          <t>En smal skadad knäckt sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Grov bark. # Salix caprea # En smal skadad knäckt sälg.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6823,10 +6814,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122226624</v>
+        <v>122193783</v>
       </c>
       <c r="B49" t="n">
-        <v>78646</v>
+        <v>79732</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6839,40 +6830,44 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514188</v>
+        <v>514670</v>
       </c>
       <c r="R49" t="n">
-        <v>7023245</v>
+        <v>7023247</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6906,7 +6901,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Garnlav på flera granar.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6926,27 +6921,32 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Äldre barrskog med en mosaik av talldominerade och grandominerade partier på frisk till fuktig mark.</t>
+          <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL49" t="inlineStr">
+        <is>
+          <t>En knäckt smal relativt grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea # En knäckt smal relativt grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6964,10 +6964,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122226449</v>
+        <v>122226624</v>
       </c>
       <c r="B50" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7007,10 +7007,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514425</v>
+        <v>514188</v>
       </c>
       <c r="R50" t="n">
-        <v>7023228</v>
+        <v>7023245</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flera granar.</t>
+          <t>Garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7062,12 +7062,12 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk till fuktig mark. Här finns både stående och liggande död ved. Kolade stubbar indikerar tidigare brandpåverkan.</t>
+          <t>Äldre barrskog med en mosaik av talldominerade och grandominerade partier på frisk till fuktig mark.</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -7105,10 +7105,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122223793</v>
+        <v>122194394</v>
       </c>
       <c r="B51" t="n">
-        <v>79727</v>
+        <v>79733</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7121,21 +7121,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -7148,17 +7148,17 @@
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sauholmen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>514631</v>
+        <v>514600</v>
       </c>
       <c r="R51" t="n">
-        <v>7023229</v>
+        <v>7023243</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7192,7 +7192,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ett par "knippen" med lunglav på en grovbarkad sälg.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7227,17 +7227,17 @@
       </c>
       <c r="AL51" t="inlineStr">
         <is>
-          <t>En något smalare men grovbarkad sälg.</t>
+          <t>En smal skadad knäckt sälg.</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea # En något smalare men grovbarkad sälg.</t>
+          <t>Bark of dead wood # Grov bark. # Salix caprea # En smal skadad knäckt sälg.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>

--- a/artfynd/A 55314-2024 artfynd.xlsx
+++ b/artfynd/A 55314-2024 artfynd.xlsx
@@ -4835,10 +4835,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122191658</v>
+        <v>122208210</v>
       </c>
       <c r="B35" t="n">
-        <v>78651</v>
+        <v>79732</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4851,37 +4851,44 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514512</v>
+        <v>514264</v>
       </c>
       <c r="R35" t="n">
-        <v>7023275</v>
+        <v>7023177</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4919,32 +4926,38 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Med inslag av gran, sälg och björk.</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4962,10 +4975,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122208029</v>
+        <v>122207795</v>
       </c>
       <c r="B36" t="n">
-        <v>57395</v>
+        <v>57379</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4978,16 +4991,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5010,14 +5023,14 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lillberget, Klenflon, Häggenås, Jmt</t>
+          <t>Sauholmen, Klenflon, Häggenås, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>514232</v>
+        <v>514641</v>
       </c>
       <c r="R36" t="n">
-        <v>7023309</v>
+        <v>7023370</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -5054,7 +5067,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska rejäla hackspår av spillkråka i basen av en gran.</t>
+          <t>Färska hackspår (ringhack), i basen av en gran, som bedöms vara skapade inom 5 år tillbaks. I området kring denna plats finns även födosökspår på stående smala döda granar.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5073,7 +5086,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Äldre skog med olikåldriga träd.</t>
+          <t>Grandominerad skog med inslag av tall och björk på frisk-fuktig och fuktig mark.</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -5088,12 +5101,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5111,10 +5124,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122193443</v>
+        <v>122192869</v>
       </c>
       <c r="B37" t="n">
-        <v>90819</v>
+        <v>78651</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5127,48 +5140,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>514671</v>
+        <v>514655</v>
       </c>
       <c r="R37" t="n">
-        <v>7023306</v>
+        <v>7023373</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5229,12 +5228,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5252,10 +5251,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122208320</v>
+        <v>122191658</v>
       </c>
       <c r="B38" t="n">
-        <v>57395</v>
+        <v>78651</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5268,45 +5267,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>514264</v>
+        <v>514512</v>
       </c>
       <c r="R38" t="n">
-        <v>7023177</v>
+        <v>7023275</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5338,11 +5329,6 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska hackspår av spillkråka i en sälg.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5354,32 +5340,27 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Med inslag av gran, sälg och björk.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Stem on living tree # Salix caprea</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5397,10 +5378,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122208128</v>
+        <v>122193443</v>
       </c>
       <c r="B39" t="n">
-        <v>79732</v>
+        <v>90826</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5413,41 +5394,48 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>514240</v>
+        <v>514671</v>
       </c>
       <c r="R39" t="n">
-        <v>7023172</v>
+        <v>7023306</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5482,54 +5470,38 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ymnig påväxt av lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>Med inslag av gran, sälg och björk.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL39" t="inlineStr">
-        <is>
-          <t>En skadad knäckt men levande sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En skadad knäckt men levande sälg.</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5547,7 +5519,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122208210</v>
+        <v>122208128</v>
       </c>
       <c r="B40" t="n">
         <v>79732</v>
@@ -5594,13 +5566,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>514264</v>
+        <v>514240</v>
       </c>
       <c r="R40" t="n">
-        <v>7023177</v>
+        <v>7023172</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5630,6 +5602,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-01-18</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ymnig påväxt av lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5662,6 +5639,11 @@
           <t>Salix caprea</t>
         </is>
       </c>
+      <c r="AL40" t="inlineStr">
+        <is>
+          <t>En skadad knäckt men levande sälg.</t>
+        </is>
+      </c>
       <c r="AM40" t="inlineStr">
         <is>
           <t>Bark på levande träd</t>
@@ -5669,7 +5651,7 @@
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea # En skadad knäckt men levande sälg.</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5808,10 +5790,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122192869</v>
+        <v>122208029</v>
       </c>
       <c r="B42" t="n">
-        <v>78651</v>
+        <v>57395</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5824,37 +5806,49 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Klenflon, Häggenås, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>514655</v>
+        <v>514232</v>
       </c>
       <c r="R42" t="n">
-        <v>7023373</v>
+        <v>7023309</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5886,6 +5880,11 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Färska rejäla hackspår av spillkråka i basen av en gran.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5897,7 +5896,12 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Äldre skog med olikåldriga träd.</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
@@ -5912,12 +5916,12 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5935,10 +5939,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122207795</v>
+        <v>122208320</v>
       </c>
       <c r="B43" t="n">
-        <v>57379</v>
+        <v>57395</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5951,16 +5955,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5976,21 +5980,17 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sauholmen, Klenflon, Häggenås, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>514641</v>
+        <v>514264</v>
       </c>
       <c r="R43" t="n">
-        <v>7023370</v>
+        <v>7023177</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -6027,7 +6027,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Färska hackspår (ringhack), i basen av en gran, som bedöms vara skapade inom 5 år tillbaks. I området kring denna plats finns även födosökspår på stående smala döda granar.</t>
+          <t>Färska hackspår av spillkråka i en sälg.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6041,22 +6041,22 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Grandominerad skog med inslag av tall och björk på frisk-fuktig och fuktig mark.</t>
+          <t>Med inslag av gran, sälg och björk.</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Salix caprea</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6234,10 +6234,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122194568</v>
+        <v>122226624</v>
       </c>
       <c r="B45" t="n">
-        <v>57379</v>
+        <v>78651</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6250,49 +6250,40 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>514580</v>
+        <v>514188</v>
       </c>
       <c r="R45" t="n">
-        <v>7023243</v>
+        <v>7023245</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6326,7 +6317,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Äldre ringhack på basen av en gran.</t>
+          <t>Garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6335,6 +6326,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6345,7 +6337,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
+          <t>Äldre barrskog med en mosaik av talldominerade och grandominerade partier på frisk till fuktig mark.</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
@@ -6360,12 +6352,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6537,10 +6529,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122194308</v>
+        <v>122194568</v>
       </c>
       <c r="B47" t="n">
-        <v>78651</v>
+        <v>57379</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6553,37 +6545,46 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>514604</v>
+        <v>514580</v>
       </c>
       <c r="R47" t="n">
-        <v>7023237</v>
+        <v>7023243</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6618,13 +6619,17 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på basen av en gran.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6650,12 +6655,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6673,10 +6678,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122226449</v>
+        <v>122194394</v>
       </c>
       <c r="B48" t="n">
-        <v>78651</v>
+        <v>79733</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6689,40 +6694,44 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>514425</v>
+        <v>514600</v>
       </c>
       <c r="R48" t="n">
-        <v>7023228</v>
+        <v>7023243</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6756,7 +6765,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flera granar.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6771,32 +6780,37 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk till fuktig mark. Här finns både stående och liggande död ved. Kolade stubbar indikerar tidigare brandpåverkan.</t>
+          <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>En smal skadad knäckt sälg.</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Grov bark. # Salix caprea # En smal skadad knäckt sälg.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6964,7 +6978,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122226624</v>
+        <v>122194308</v>
       </c>
       <c r="B50" t="n">
         <v>78651</v>
@@ -7003,17 +7017,17 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514188</v>
+        <v>514604</v>
       </c>
       <c r="R50" t="n">
-        <v>7023245</v>
+        <v>7023237</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7043,11 +7057,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-01-18</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7067,7 +7076,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Äldre barrskog med en mosaik av talldominerade och grandominerade partier på frisk till fuktig mark.</t>
+          <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -7105,10 +7114,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122194394</v>
+        <v>122226449</v>
       </c>
       <c r="B51" t="n">
-        <v>79733</v>
+        <v>78651</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7121,44 +7130,40 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>514600</v>
+        <v>514425</v>
       </c>
       <c r="R51" t="n">
-        <v>7023243</v>
+        <v>7023228</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7192,7 +7197,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>Långväxt garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7207,37 +7212,32 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk till fuktig mark. Här finns både stående och liggande död ved. Kolade stubbar indikerar tidigare brandpåverkan.</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL51" t="inlineStr">
-        <is>
-          <t>En smal skadad knäckt sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Grov bark. # Salix caprea # En smal skadad knäckt sälg.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>

--- a/artfynd/A 55314-2024 artfynd.xlsx
+++ b/artfynd/A 55314-2024 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>121667141</v>
       </c>
       <c r="B3" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,11 +819,6 @@
       </c>
       <c r="E3" t="n">
         <v>6458</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -910,11 +905,6 @@
       <c r="AI3" t="inlineStr">
         <is>
           <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>sälg</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1097,11 +1087,6 @@
       <c r="E5" t="n">
         <v>100109</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -1187,11 +1172,6 @@
       <c r="AI5" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk till fuktig mark. Här finns både stående och liggande död ved.</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1817,7 +1797,7 @@
         <v>121667143</v>
       </c>
       <c r="B11" t="n">
-        <v>79761</v>
+        <v>79762</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1831,11 +1811,6 @@
       </c>
       <c r="E11" t="n">
         <v>6462</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Stuplav</t>
-        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1917,11 +1892,6 @@
       <c r="AI11" t="inlineStr">
         <is>
           <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>sälg</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3142,11 +3112,6 @@
       <c r="E22" t="n">
         <v>100109</v>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -3232,11 +3197,6 @@
       <c r="AI22" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk till fuktig mark. Här finns både stående och liggande död ved.</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -4028,7 +3988,7 @@
         <v>121667163</v>
       </c>
       <c r="B29" t="n">
-        <v>79767</v>
+        <v>79768</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4042,11 +4002,6 @@
       </c>
       <c r="E29" t="n">
         <v>6463</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Bårdlav</t>
-        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -4126,11 +4081,6 @@
           <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
         </is>
       </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
       <c r="AK29" t="inlineStr">
         <is>
           <t>Salix caprea</t>
@@ -4179,11 +4129,6 @@
       <c r="E30" t="n">
         <v>100109</v>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -4269,11 +4214,6 @@
       <c r="AI30" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk till fuktig mark. Här finns både stående och liggande död ved.</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -4436,7 +4376,7 @@
         <v>121667243</v>
       </c>
       <c r="B32" t="n">
-        <v>79768</v>
+        <v>79769</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4450,11 +4390,6 @@
       </c>
       <c r="E32" t="n">
         <v>6464</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Luddlav</t>
-        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -4541,11 +4476,6 @@
       <c r="AI32" t="inlineStr">
         <is>
           <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>sälg</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -4688,7 +4618,7 @@
         <v>121667142</v>
       </c>
       <c r="B34" t="n">
-        <v>79733</v>
+        <v>79734</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4702,11 +4632,6 @@
       </c>
       <c r="E34" t="n">
         <v>2081</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -4793,11 +4718,6 @@
       <c r="AI34" t="inlineStr">
         <is>
           <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>sälg</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -4835,10 +4755,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122208210</v>
+        <v>122192869</v>
       </c>
       <c r="B35" t="n">
-        <v>79732</v>
+        <v>78652</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4851,44 +4771,32 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514264</v>
+        <v>514655</v>
       </c>
       <c r="R35" t="n">
-        <v>7023177</v>
+        <v>7023373</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4926,38 +4834,27 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Med inslag av gran, sälg och björk.</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>sälg</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4975,10 +4872,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122207795</v>
+        <v>122208128</v>
       </c>
       <c r="B36" t="n">
-        <v>57379</v>
+        <v>79733</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4991,49 +4888,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sauholmen, Klenflon, Häggenås, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>514641</v>
+        <v>514240</v>
       </c>
       <c r="R36" t="n">
-        <v>7023370</v>
+        <v>7023172</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5067,7 +4954,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska hackspår (ringhack), i basen av en gran, som bedöms vara skapade inom 5 år tillbaks. I området kring denna plats finns även födosökspår på stående smala döda granar.</t>
+          <t>Ymnig påväxt av lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5076,37 +4963,38 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Grandominerad skog med inslag av tall och björk på frisk-fuktig och fuktig mark.</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
+          <t>Med inslag av gran, sälg och björk.</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL36" t="inlineStr">
+        <is>
+          <t>En skadad knäckt men levande sälg.</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En skadad knäckt men levande sälg.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5124,10 +5012,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122192869</v>
+        <v>122208320</v>
       </c>
       <c r="B37" t="n">
-        <v>78651</v>
+        <v>57395</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5140,37 +5028,40 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>514655</v>
+        <v>514264</v>
       </c>
       <c r="R37" t="n">
-        <v>7023373</v>
+        <v>7023177</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5202,6 +5093,11 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska hackspår av spillkråka i en sälg.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5213,27 +5109,27 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Med inslag av gran, sälg och björk.</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Salix caprea</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5254,7 +5150,7 @@
         <v>122191658</v>
       </c>
       <c r="B38" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5269,11 +5165,6 @@
       <c r="E38" t="n">
         <v>6425</v>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -5341,11 +5232,6 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -5381,7 +5267,7 @@
         <v>122193443</v>
       </c>
       <c r="B39" t="n">
-        <v>90826</v>
+        <v>90831</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5396,11 +5282,6 @@
       <c r="E39" t="n">
         <v>5432</v>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>Porodaedalea chrysoloma</t>
@@ -5482,11 +5363,6 @@
       <c r="AH39" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -5519,10 +5395,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122208128</v>
+        <v>122208029</v>
       </c>
       <c r="B40" t="n">
-        <v>79732</v>
+        <v>57395</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5535,44 +5411,44 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Lillberget, Klenflon, Häggenås, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>514240</v>
+        <v>514232</v>
       </c>
       <c r="R40" t="n">
-        <v>7023172</v>
+        <v>7023309</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5606,7 +5482,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ymnig påväxt av lunglav på sälg.</t>
+          <t>Färska rejäla hackspår av spillkråka i basen av en gran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5615,43 +5491,32 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Med inslag av gran, sälg och björk.</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>sälg</t>
+          <t>Äldre skog med olikåldriga träd.</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL40" t="inlineStr">
-        <is>
-          <t>En skadad knäckt men levande sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En skadad knäckt men levande sälg.</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5669,10 +5534,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122193236</v>
+        <v>122208210</v>
       </c>
       <c r="B41" t="n">
-        <v>57532</v>
+        <v>79733</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5685,51 +5550,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>514622</v>
+        <v>514264</v>
       </c>
       <c r="R41" t="n">
-        <v>7023310</v>
+        <v>7023177</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5767,12 +5620,33 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Med inslag av gran, sälg och björk.</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5790,10 +5664,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122208029</v>
+        <v>122207795</v>
       </c>
       <c r="B42" t="n">
-        <v>57395</v>
+        <v>57379</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5806,16 +5680,11 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5838,14 +5707,14 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lillberget, Klenflon, Häggenås, Jmt</t>
+          <t>Sauholmen, Klenflon, Häggenås, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>514232</v>
+        <v>514641</v>
       </c>
       <c r="R42" t="n">
-        <v>7023309</v>
+        <v>7023370</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5882,7 +5751,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Färska rejäla hackspår av spillkråka i basen av en gran.</t>
+          <t>Färska hackspår (ringhack), i basen av en gran, som bedöms vara skapade inom 5 år tillbaks. I området kring denna plats finns även födosökspår på stående smala döda granar.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5901,12 +5770,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Äldre skog med olikåldriga träd.</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
+          <t>Grandominerad skog med inslag av tall och björk på frisk-fuktig och fuktig mark.</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -5916,12 +5780,12 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5939,10 +5803,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122208320</v>
+        <v>122193236</v>
       </c>
       <c r="B43" t="n">
-        <v>57395</v>
+        <v>57532</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5955,45 +5819,46 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>103021</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>514264</v>
+        <v>514622</v>
       </c>
       <c r="R43" t="n">
-        <v>7023177</v>
+        <v>7023310</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6025,11 +5890,6 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Färska hackspår av spillkråka i en sälg.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -6041,32 +5901,7 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>Med inslag av gran, sälg och björk.</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Salix caprea</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6084,10 +5919,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122223793</v>
+        <v>122194308</v>
       </c>
       <c r="B44" t="n">
-        <v>79732</v>
+        <v>78652</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6100,44 +5935,35 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>6425</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sauholmen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>514631</v>
+        <v>514604</v>
       </c>
       <c r="R44" t="n">
-        <v>7023229</v>
+        <v>7023237</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6167,11 +5993,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-01-18</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ett par "knippen" med lunglav på en grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6194,29 +6015,19 @@
           <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
         </is>
       </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL44" t="inlineStr">
-        <is>
-          <t>En något smalare men grovbarkad sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea # En något smalare men grovbarkad sälg.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6237,7 +6048,7 @@
         <v>122226624</v>
       </c>
       <c r="B45" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6251,11 +6062,6 @@
       </c>
       <c r="E45" t="n">
         <v>6425</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -6340,11 +6146,6 @@
           <t>Äldre barrskog med en mosaik av talldominerade och grandominerade partier på frisk till fuktig mark.</t>
         </is>
       </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK45" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -6393,11 +6194,6 @@
       <c r="E46" t="n">
         <v>100049</v>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
       <c r="G46" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>
@@ -6489,11 +6285,6 @@
           <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
         </is>
       </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
       <c r="AK46" t="inlineStr">
         <is>
           <t>Populus tremula</t>
@@ -6529,10 +6320,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122194568</v>
+        <v>122193783</v>
       </c>
       <c r="B47" t="n">
-        <v>57379</v>
+        <v>79733</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6545,46 +6336,36 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6458</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>514580</v>
+        <v>514670</v>
       </c>
       <c r="R47" t="n">
-        <v>7023243</v>
+        <v>7023247</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6621,7 +6402,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Äldre ringhack på basen av en gran.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6630,6 +6411,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6643,24 +6425,24 @@
           <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
         </is>
       </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL47" t="inlineStr">
+        <is>
+          <t>En knäckt smal relativt grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea # En knäckt smal relativt grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6678,10 +6460,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122194394</v>
+        <v>122194568</v>
       </c>
       <c r="B48" t="n">
-        <v>79733</v>
+        <v>57379</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6694,38 +6476,38 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>514600</v>
+        <v>514580</v>
       </c>
       <c r="R48" t="n">
         <v>7023243</v>
@@ -6765,7 +6547,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>Äldre ringhack på basen av en gran.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6774,7 +6556,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6788,29 +6569,19 @@
           <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
         </is>
       </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL48" t="inlineStr">
-        <is>
-          <t>En smal skadad knäckt sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Grov bark. # Salix caprea # En smal skadad knäckt sälg.</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6828,10 +6599,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122193783</v>
+        <v>122223793</v>
       </c>
       <c r="B49" t="n">
-        <v>79732</v>
+        <v>79733</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6845,11 +6616,6 @@
       </c>
       <c r="E49" t="n">
         <v>6458</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -6871,17 +6637,17 @@
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514670</v>
+        <v>514631</v>
       </c>
       <c r="R49" t="n">
-        <v>7023247</v>
+        <v>7023229</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6915,7 +6681,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>Ett par "knippen" med lunglav på en grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6938,11 +6704,6 @@
           <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
         </is>
       </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
       <c r="AK49" t="inlineStr">
         <is>
           <t>Salix caprea</t>
@@ -6950,17 +6711,17 @@
       </c>
       <c r="AL49" t="inlineStr">
         <is>
-          <t>En knäckt smal relativt grovbarkad sälg.</t>
+          <t>En något smalare men grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En knäckt smal relativt grovbarkad sälg.</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En något smalare men grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6978,10 +6739,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122194308</v>
+        <v>122226449</v>
       </c>
       <c r="B50" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6995,11 +6756,6 @@
       </c>
       <c r="E50" t="n">
         <v>6425</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -7017,17 +6773,17 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514604</v>
+        <v>514425</v>
       </c>
       <c r="R50" t="n">
-        <v>7023237</v>
+        <v>7023228</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7057,6 +6813,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-01-18</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Långväxt garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7071,17 +6832,12 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk till fuktig mark. Här finns både stående och liggande död ved. Kolade stubbar indikerar tidigare brandpåverkan.</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -7114,10 +6870,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122226449</v>
+        <v>122194394</v>
       </c>
       <c r="B51" t="n">
-        <v>78651</v>
+        <v>79734</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7130,40 +6886,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>2081</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>514425</v>
+        <v>514600</v>
       </c>
       <c r="R51" t="n">
-        <v>7023228</v>
+        <v>7023243</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7197,7 +6952,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flera granar.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7212,32 +6967,32 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk till fuktig mark. Här finns både stående och liggande död ved. Kolade stubbar indikerar tidigare brandpåverkan.</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
+          <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL51" t="inlineStr">
+        <is>
+          <t>En smal skadad knäckt sälg.</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Grov bark. # Salix caprea # En smal skadad knäckt sälg.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>

--- a/artfynd/A 55314-2024 artfynd.xlsx
+++ b/artfynd/A 55314-2024 artfynd.xlsx
@@ -4755,10 +4755,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122192869</v>
+        <v>122208320</v>
       </c>
       <c r="B35" t="n">
-        <v>78652</v>
+        <v>57395</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4771,32 +4771,40 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514655</v>
+        <v>514264</v>
       </c>
       <c r="R35" t="n">
-        <v>7023373</v>
+        <v>7023177</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4828,6 +4836,11 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska hackspår av spillkråka i en sälg.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4839,22 +4852,27 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Med inslag av gran, sälg och björk.</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Salix caprea</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5012,10 +5030,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122208320</v>
+        <v>122192869</v>
       </c>
       <c r="B37" t="n">
-        <v>57395</v>
+        <v>78652</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5028,40 +5046,32 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>514264</v>
+        <v>514655</v>
       </c>
       <c r="R37" t="n">
-        <v>7023177</v>
+        <v>7023373</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5093,11 +5103,6 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska hackspår av spillkråka i en sälg.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5109,27 +5114,22 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>Med inslag av gran, sälg och björk.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>

--- a/artfynd/A 55314-2024 artfynd.xlsx
+++ b/artfynd/A 55314-2024 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>121667141</v>
       </c>
       <c r="B3" t="n">
-        <v>79733</v>
+        <v>79737</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,6 +819,11 @@
       </c>
       <c r="E3" t="n">
         <v>6458</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -905,6 +910,11 @@
       <c r="AI3" t="inlineStr">
         <is>
           <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1072,7 +1082,7 @@
         <v>121669062</v>
       </c>
       <c r="B5" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1086,6 +1096,11 @@
       </c>
       <c r="E5" t="n">
         <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1172,6 +1187,11 @@
       <c r="AI5" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk till fuktig mark. Här finns både stående och liggande död ved.</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1797,7 +1817,7 @@
         <v>121667143</v>
       </c>
       <c r="B11" t="n">
-        <v>79762</v>
+        <v>79766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1811,6 +1831,11 @@
       </c>
       <c r="E11" t="n">
         <v>6462</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1892,6 +1917,11 @@
       <c r="AI11" t="inlineStr">
         <is>
           <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3097,7 +3127,7 @@
         <v>121669887</v>
       </c>
       <c r="B22" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3111,6 +3141,11 @@
       </c>
       <c r="E22" t="n">
         <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -3197,6 +3232,11 @@
       <c r="AI22" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk till fuktig mark. Här finns både stående och liggande död ved.</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -3988,7 +4028,7 @@
         <v>121667163</v>
       </c>
       <c r="B29" t="n">
-        <v>79768</v>
+        <v>79772</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4002,6 +4042,11 @@
       </c>
       <c r="E29" t="n">
         <v>6463</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -4081,6 +4126,11 @@
           <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
         </is>
       </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
       <c r="AK29" t="inlineStr">
         <is>
           <t>Salix caprea</t>
@@ -4114,7 +4164,7 @@
         <v>121669055</v>
       </c>
       <c r="B30" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4128,6 +4178,11 @@
       </c>
       <c r="E30" t="n">
         <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -4214,6 +4269,11 @@
       <c r="AI30" t="inlineStr">
         <is>
           <t>Grandominerad gammal skog med olikåldriga träd på frisk till fuktig mark. Här finns både stående och liggande död ved.</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -4376,7 +4436,7 @@
         <v>121667243</v>
       </c>
       <c r="B32" t="n">
-        <v>79769</v>
+        <v>79773</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4390,6 +4450,11 @@
       </c>
       <c r="E32" t="n">
         <v>6464</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -4476,6 +4541,11 @@
       <c r="AI32" t="inlineStr">
         <is>
           <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -4618,7 +4688,7 @@
         <v>121667142</v>
       </c>
       <c r="B34" t="n">
-        <v>79734</v>
+        <v>79738</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4632,6 +4702,11 @@
       </c>
       <c r="E34" t="n">
         <v>2081</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -4718,6 +4793,11 @@
       <c r="AI34" t="inlineStr">
         <is>
           <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -4755,10 +4835,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122208320</v>
+        <v>122193443</v>
       </c>
       <c r="B35" t="n">
-        <v>57395</v>
+        <v>90844</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4771,40 +4851,51 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>5432</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514264</v>
+        <v>514671</v>
       </c>
       <c r="R35" t="n">
-        <v>7023177</v>
+        <v>7023306</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4836,11 +4927,6 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Färska hackspår av spillkråka i en sälg.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4852,17 +4938,17 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Med inslag av gran, sälg och björk.</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
@@ -4872,7 +4958,7 @@
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Stem on living tree # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4890,10 +4976,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122208128</v>
+        <v>122208029</v>
       </c>
       <c r="B36" t="n">
-        <v>79733</v>
+        <v>57399</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4906,39 +4992,49 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100049</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Lillberget, Klenflon, Häggenås, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>514240</v>
+        <v>514232</v>
       </c>
       <c r="R36" t="n">
-        <v>7023172</v>
+        <v>7023309</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4972,7 +5068,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ymnig påväxt av lunglav på sälg.</t>
+          <t>Färska rejäla hackspår av spillkråka i basen av en gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4981,38 +5077,37 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Med inslag av gran, sälg och björk.</t>
+          <t>Äldre skog med olikåldriga träd.</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL36" t="inlineStr">
-        <is>
-          <t>En skadad knäckt men levande sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En skadad knäckt men levande sälg.</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5030,10 +5125,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122192869</v>
+        <v>122208210</v>
       </c>
       <c r="B37" t="n">
-        <v>78652</v>
+        <v>79737</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5046,32 +5141,44 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>514655</v>
+        <v>514264</v>
       </c>
       <c r="R37" t="n">
-        <v>7023373</v>
+        <v>7023177</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5109,27 +5216,38 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Med inslag av gran, sälg och björk.</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5150,7 +5268,7 @@
         <v>122191658</v>
       </c>
       <c r="B38" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5165,6 +5283,11 @@
       <c r="E38" t="n">
         <v>6425</v>
       </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>Alectoria sarmentosa</t>
@@ -5232,6 +5355,11 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -5264,10 +5392,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122193443</v>
+        <v>122192869</v>
       </c>
       <c r="B39" t="n">
-        <v>90831</v>
+        <v>78656</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5280,43 +5408,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>514671</v>
+        <v>514655</v>
       </c>
       <c r="R39" t="n">
-        <v>7023306</v>
+        <v>7023373</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5365,6 +5484,11 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK39" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -5372,12 +5496,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5395,10 +5519,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122208029</v>
+        <v>122207795</v>
       </c>
       <c r="B40" t="n">
-        <v>57395</v>
+        <v>57383</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5411,11 +5535,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5438,14 +5567,14 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lillberget, Klenflon, Häggenås, Jmt</t>
+          <t>Sauholmen, Klenflon, Häggenås, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>514232</v>
+        <v>514641</v>
       </c>
       <c r="R40" t="n">
-        <v>7023309</v>
+        <v>7023370</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5482,7 +5611,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Färska rejäla hackspår av spillkråka i basen av en gran.</t>
+          <t>Färska hackspår (ringhack), i basen av en gran, som bedöms vara skapade inom 5 år tillbaks. I området kring denna plats finns även födosökspår på stående smala döda granar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5501,7 +5630,12 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Äldre skog med olikåldriga träd.</t>
+          <t>Grandominerad skog med inslag av tall och björk på frisk-fuktig och fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -5511,12 +5645,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5534,10 +5668,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122208210</v>
+        <v>122193236</v>
       </c>
       <c r="B41" t="n">
-        <v>79733</v>
+        <v>57536</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5550,39 +5684,51 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>103021</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>514264</v>
+        <v>514622</v>
       </c>
       <c r="R41" t="n">
-        <v>7023177</v>
+        <v>7023310</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5620,33 +5766,12 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>Med inslag av gran, sälg och björk.</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5664,10 +5789,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122207795</v>
+        <v>122208320</v>
       </c>
       <c r="B42" t="n">
-        <v>57379</v>
+        <v>57399</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5680,11 +5805,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>100049</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5700,21 +5830,17 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sauholmen, Klenflon, Häggenås, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>514641</v>
+        <v>514264</v>
       </c>
       <c r="R42" t="n">
-        <v>7023370</v>
+        <v>7023177</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5751,7 +5877,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Färska hackspår (ringhack), i basen av en gran, som bedöms vara skapade inom 5 år tillbaks. I området kring denna plats finns även födosökspår på stående smala döda granar.</t>
+          <t>Färska hackspår av spillkråka i en sälg.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5765,17 +5891,22 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Grandominerad skog med inslag av tall och björk på frisk-fuktig och fuktig mark.</t>
+          <t>Med inslag av gran, sälg och björk.</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
@@ -5785,7 +5916,7 @@
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5803,10 +5934,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122193236</v>
+        <v>122208128</v>
       </c>
       <c r="B43" t="n">
-        <v>57532</v>
+        <v>79737</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5819,43 +5950,41 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>6458</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>514622</v>
+        <v>514240</v>
       </c>
       <c r="R43" t="n">
-        <v>7023310</v>
+        <v>7023172</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5890,18 +6019,54 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ymnig påväxt av lunglav på sälg.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Med inslag av gran, sälg och björk.</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL43" t="inlineStr">
+        <is>
+          <t>En skadad knäckt men levande sälg.</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea # En skadad knäckt men levande sälg.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5919,10 +6084,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122194308</v>
+        <v>122226449</v>
       </c>
       <c r="B44" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5936,6 +6101,11 @@
       </c>
       <c r="E44" t="n">
         <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -5953,17 +6123,17 @@
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>514604</v>
+        <v>514425</v>
       </c>
       <c r="R44" t="n">
-        <v>7023237</v>
+        <v>7023228</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5993,6 +6163,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-01-18</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Långväxt garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6007,12 +6182,17 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk till fuktig mark. Här finns både stående och liggande död ved. Kolade stubbar indikerar tidigare brandpåverkan.</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -6045,10 +6225,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122226624</v>
+        <v>122223793</v>
       </c>
       <c r="B45" t="n">
-        <v>78652</v>
+        <v>79737</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6061,32 +6241,41 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>514188</v>
+        <v>514631</v>
       </c>
       <c r="R45" t="n">
-        <v>7023245</v>
+        <v>7023229</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -6123,7 +6312,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Garnlav på flera granar.</t>
+          <t>Ett par "knippen" med lunglav på en grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6143,22 +6332,32 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Äldre barrskog med en mosaik av talldominerade och grandominerade partier på frisk till fuktig mark.</t>
+          <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL45" t="inlineStr">
+        <is>
+          <t>En något smalare men grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En något smalare men grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6179,7 +6378,7 @@
         <v>122223410</v>
       </c>
       <c r="B46" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6193,6 +6392,11 @@
       </c>
       <c r="E46" t="n">
         <v>100049</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -6285,6 +6489,11 @@
           <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
         </is>
       </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
       <c r="AK46" t="inlineStr">
         <is>
           <t>Populus tremula</t>
@@ -6320,10 +6529,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122193783</v>
+        <v>122194308</v>
       </c>
       <c r="B47" t="n">
-        <v>79733</v>
+        <v>78656</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6336,36 +6545,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>514670</v>
+        <v>514604</v>
       </c>
       <c r="R47" t="n">
-        <v>7023247</v>
+        <v>7023237</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6400,11 +6610,6 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6425,24 +6630,24 @@
           <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
         </is>
       </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL47" t="inlineStr">
-        <is>
-          <t>En knäckt smal relativt grovbarkad sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En knäckt smal relativt grovbarkad sälg.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6463,7 +6668,7 @@
         <v>122194568</v>
       </c>
       <c r="B48" t="n">
-        <v>57379</v>
+        <v>57383</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6477,6 +6682,11 @@
       </c>
       <c r="E48" t="n">
         <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -6569,6 +6779,11 @@
           <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
         </is>
       </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AK48" t="inlineStr">
         <is>
           <t>Picea abies</t>
@@ -6599,10 +6814,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122223793</v>
+        <v>122193783</v>
       </c>
       <c r="B49" t="n">
-        <v>79733</v>
+        <v>79737</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6616,6 +6831,11 @@
       </c>
       <c r="E49" t="n">
         <v>6458</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -6637,17 +6857,17 @@
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sauholmen, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514631</v>
+        <v>514670</v>
       </c>
       <c r="R49" t="n">
-        <v>7023229</v>
+        <v>7023247</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6681,7 +6901,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ett par "knippen" med lunglav på en grovbarkad sälg.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6704,6 +6924,11 @@
           <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
         </is>
       </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
       <c r="AK49" t="inlineStr">
         <is>
           <t>Salix caprea</t>
@@ -6711,17 +6936,17 @@
       </c>
       <c r="AL49" t="inlineStr">
         <is>
-          <t>En något smalare men grovbarkad sälg.</t>
+          <t>En knäckt smal relativt grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea # En något smalare men grovbarkad sälg.</t>
+          <t>Bark of dead wood # Salix caprea # En knäckt smal relativt grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6739,10 +6964,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122226449</v>
+        <v>122226624</v>
       </c>
       <c r="B50" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6756,6 +6981,11 @@
       </c>
       <c r="E50" t="n">
         <v>6425</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -6777,10 +7007,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514425</v>
+        <v>514188</v>
       </c>
       <c r="R50" t="n">
-        <v>7023228</v>
+        <v>7023245</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6817,7 +7047,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flera granar.</t>
+          <t>Garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6832,12 +7062,17 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk till fuktig mark. Här finns både stående och liggande död ved. Kolade stubbar indikerar tidigare brandpåverkan.</t>
+          <t>Äldre barrskog med en mosaik av talldominerade och grandominerade partier på frisk till fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -6873,7 +7108,7 @@
         <v>122194394</v>
       </c>
       <c r="B51" t="n">
-        <v>79734</v>
+        <v>79738</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6887,6 +7122,11 @@
       </c>
       <c r="E51" t="n">
         <v>2081</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -6973,6 +7213,11 @@
       <c r="AI51" t="inlineStr">
         <is>
           <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">

--- a/artfynd/A 55314-2024 artfynd.xlsx
+++ b/artfynd/A 55314-2024 artfynd.xlsx
@@ -4835,10 +4835,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122193443</v>
+        <v>122208029</v>
       </c>
       <c r="B35" t="n">
-        <v>90844</v>
+        <v>57399</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4851,51 +4851,49 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Klenflon, Häggenås, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514671</v>
+        <v>514232</v>
       </c>
       <c r="R35" t="n">
-        <v>7023306</v>
+        <v>7023309</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4927,6 +4925,11 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska rejäla hackspår av spillkråka i basen av en gran.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4938,7 +4941,12 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Äldre skog med olikåldriga träd.</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -4953,12 +4961,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4976,10 +4984,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122208029</v>
+        <v>122191658</v>
       </c>
       <c r="B36" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4992,49 +5000,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lillberget, Klenflon, Häggenås, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>514232</v>
+        <v>514512</v>
       </c>
       <c r="R36" t="n">
-        <v>7023309</v>
+        <v>7023275</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5066,11 +5062,6 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Färska rejäla hackspår av spillkråka i basen av en gran.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -5082,12 +5073,7 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>Äldre skog med olikåldriga träd.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -5102,12 +5088,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5125,10 +5111,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122208210</v>
+        <v>122207795</v>
       </c>
       <c r="B37" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5141,41 +5127,46 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Sauholmen, Klenflon, Häggenås, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>514264</v>
+        <v>514641</v>
       </c>
       <c r="R37" t="n">
-        <v>7023177</v>
+        <v>7023370</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5210,44 +5201,48 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska hackspår (ringhack), i basen av en gran, som bedöms vara skapade inom 5 år tillbaks. I området kring denna plats finns även födosökspår på stående smala döda granar.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Med inslag av gran, sälg och björk.</t>
+          <t>Grandominerad skog med inslag av tall och björk på frisk-fuktig och fuktig mark.</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5265,10 +5260,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122191658</v>
+        <v>122208210</v>
       </c>
       <c r="B38" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5281,37 +5276,44 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>514512</v>
+        <v>514264</v>
       </c>
       <c r="R38" t="n">
-        <v>7023275</v>
+        <v>7023177</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5349,32 +5351,38 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Med inslag av gran, sälg och björk.</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5392,10 +5400,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122192869</v>
+        <v>122208320</v>
       </c>
       <c r="B39" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5408,37 +5416,45 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>514655</v>
+        <v>514264</v>
       </c>
       <c r="R39" t="n">
-        <v>7023373</v>
+        <v>7023177</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5470,6 +5486,11 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska hackspår av spillkråka i en sälg.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5481,27 +5502,32 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Med inslag av gran, sälg och björk.</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Salix caprea</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5519,10 +5545,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122207795</v>
+        <v>122193236</v>
       </c>
       <c r="B40" t="n">
-        <v>57383</v>
+        <v>57536</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5535,29 +5561,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5567,17 +5595,17 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sauholmen, Klenflon, Häggenås, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>514641</v>
+        <v>514622</v>
       </c>
       <c r="R40" t="n">
-        <v>7023370</v>
+        <v>7023310</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5609,11 +5637,6 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färska hackspår (ringhack), i basen av en gran, som bedöms vara skapade inom 5 år tillbaks. I området kring denna plats finns även födosökspår på stående smala döda granar.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5625,32 +5648,7 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall och björk på frisk-fuktig och fuktig mark.</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5668,10 +5666,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122193236</v>
+        <v>122193443</v>
       </c>
       <c r="B41" t="n">
-        <v>57536</v>
+        <v>90857</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5684,21 +5682,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5706,14 +5704,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5722,10 +5720,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>514622</v>
+        <v>514671</v>
       </c>
       <c r="R41" t="n">
-        <v>7023310</v>
+        <v>7023306</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5772,6 +5770,26 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5789,10 +5807,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122208320</v>
+        <v>122192869</v>
       </c>
       <c r="B42" t="n">
-        <v>57399</v>
+        <v>78656</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5805,45 +5823,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>514264</v>
+        <v>514655</v>
       </c>
       <c r="R42" t="n">
-        <v>7023177</v>
+        <v>7023373</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5875,11 +5885,6 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Färska hackspår av spillkråka i en sälg.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5891,32 +5896,27 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Med inslag av gran, sälg och björk.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Stem on living tree # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6084,7 +6084,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122226449</v>
+        <v>122226624</v>
       </c>
       <c r="B44" t="n">
         <v>78656</v>
@@ -6127,10 +6127,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>514425</v>
+        <v>514188</v>
       </c>
       <c r="R44" t="n">
-        <v>7023228</v>
+        <v>7023245</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flera granar.</t>
+          <t>Garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk till fuktig mark. Här finns både stående och liggande död ved. Kolade stubbar indikerar tidigare brandpåverkan.</t>
+          <t>Äldre barrskog med en mosaik av talldominerade och grandominerade partier på frisk till fuktig mark.</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -6225,10 +6225,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122223793</v>
+        <v>122194308</v>
       </c>
       <c r="B45" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6241,44 +6241,40 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sauholmen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>514631</v>
+        <v>514604</v>
       </c>
       <c r="R45" t="n">
-        <v>7023229</v>
+        <v>7023237</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6308,11 +6304,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-01-18</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ett par "knippen" med lunglav på en grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6337,27 +6328,22 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL45" t="inlineStr">
-        <is>
-          <t>En något smalare men grovbarkad sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea # En något smalare men grovbarkad sälg.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6375,10 +6361,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122223410</v>
+        <v>122194568</v>
       </c>
       <c r="B46" t="n">
-        <v>57399</v>
+        <v>57383</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6391,16 +6377,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -6413,7 +6399,7 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -6423,17 +6409,17 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sauholmen, Klenflon, Häggenås, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>514617</v>
+        <v>514580</v>
       </c>
       <c r="R46" t="n">
-        <v>7023224</v>
+        <v>7023243</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6467,7 +6453,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Relativt nyligen använt bohål på ca 4 meters höjd i en delvis skadad och hålig asp.</t>
+          <t>Äldre ringhack på basen av en gran.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6491,17 +6477,12 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AL46" t="inlineStr">
-        <is>
-          <t>En asp med uppskattningvis minst 30 cm i brösthöjdsdiameter. I trädets stam finns även fler håligheter och en uthackad skada i trädets stambas.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
@@ -6511,7 +6492,7 @@
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Stem on living tree # Populus tremula # En asp med uppskattningvis minst 30 cm i brösthöjdsdiameter. I trädets stam finns även fler håligheter och en uthackad skada i trädets stambas.</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6529,10 +6510,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122194308</v>
+        <v>122194394</v>
       </c>
       <c r="B47" t="n">
-        <v>78656</v>
+        <v>79738</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6545,26 +6526,30 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6572,10 +6557,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>514604</v>
+        <v>514600</v>
       </c>
       <c r="R47" t="n">
-        <v>7023237</v>
+        <v>7023243</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6610,6 +6595,11 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6632,22 +6622,27 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL47" t="inlineStr">
+        <is>
+          <t>En smal skadad knäckt sälg.</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Grov bark. # Salix caprea # En smal skadad knäckt sälg.</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6665,10 +6660,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122194568</v>
+        <v>122193783</v>
       </c>
       <c r="B48" t="n">
-        <v>57383</v>
+        <v>79737</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6681,46 +6676,41 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>514580</v>
+        <v>514670</v>
       </c>
       <c r="R48" t="n">
-        <v>7023243</v>
+        <v>7023247</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6757,7 +6747,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Äldre ringhack på basen av en gran.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6766,6 +6756,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6781,22 +6772,27 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>En knäckt smal relativt grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea # En knäckt smal relativt grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6814,10 +6810,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122193783</v>
+        <v>122226449</v>
       </c>
       <c r="B49" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6830,44 +6826,40 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514670</v>
+        <v>514425</v>
       </c>
       <c r="R49" t="n">
-        <v>7023247</v>
+        <v>7023228</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6901,7 +6893,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>Långväxt garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6916,37 +6908,32 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk till fuktig mark. Här finns både stående och liggande död ved. Kolade stubbar indikerar tidigare brandpåverkan.</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL49" t="inlineStr">
-        <is>
-          <t>En knäckt smal relativt grovbarkad sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En knäckt smal relativt grovbarkad sälg.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6964,10 +6951,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122226624</v>
+        <v>122223793</v>
       </c>
       <c r="B50" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6980,37 +6967,41 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514188</v>
+        <v>514631</v>
       </c>
       <c r="R50" t="n">
-        <v>7023245</v>
+        <v>7023229</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -7047,7 +7038,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Garnlav på flera granar.</t>
+          <t>Ett par "knippen" med lunglav på en grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7067,27 +7058,32 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Äldre barrskog med en mosaik av talldominerade och grandominerade partier på frisk till fuktig mark.</t>
+          <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL50" t="inlineStr">
+        <is>
+          <t>En något smalare men grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En något smalare men grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7105,14 +7101,14 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122194394</v>
+        <v>122223410</v>
       </c>
       <c r="B51" t="n">
-        <v>79738</v>
+        <v>57399</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7121,44 +7117,49 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Klenflon, Häggenås, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>514600</v>
+        <v>514617</v>
       </c>
       <c r="R51" t="n">
-        <v>7023243</v>
+        <v>7023224</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7192,7 +7193,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>Relativt nyligen använt bohål på ca 4 meters höjd i en delvis skadad och hålig asp.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7201,7 +7202,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -7217,27 +7217,27 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AL51" t="inlineStr">
         <is>
-          <t>En smal skadad knäckt sälg.</t>
+          <t>En asp med uppskattningvis minst 30 cm i brösthöjdsdiameter. I trädets stam finns även fler håligheter och en uthackad skada i trädets stambas.</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Grov bark. # Salix caprea # En smal skadad knäckt sälg.</t>
+          <t>Stem on living tree # Populus tremula # En asp med uppskattningvis minst 30 cm i brösthöjdsdiameter. I trädets stam finns även fler håligheter och en uthackad skada i trädets stambas.</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>

--- a/artfynd/A 55314-2024 artfynd.xlsx
+++ b/artfynd/A 55314-2024 artfynd.xlsx
@@ -4984,10 +4984,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122191658</v>
+        <v>122208210</v>
       </c>
       <c r="B36" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5000,37 +5000,44 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>514512</v>
+        <v>514264</v>
       </c>
       <c r="R36" t="n">
-        <v>7023275</v>
+        <v>7023177</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5068,32 +5075,38 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Med inslag av gran, sälg och björk.</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5111,10 +5124,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122207795</v>
+        <v>122193443</v>
       </c>
       <c r="B37" t="n">
-        <v>57383</v>
+        <v>90857</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5127,49 +5140,51 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sauholmen, Klenflon, Häggenås, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>514641</v>
+        <v>514671</v>
       </c>
       <c r="R37" t="n">
-        <v>7023370</v>
+        <v>7023306</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5201,11 +5216,6 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska hackspår (ringhack), i basen av en gran, som bedöms vara skapade inom 5 år tillbaks. I området kring denna plats finns även födosökspår på stående smala döda granar.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5217,12 +5227,7 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med inslag av tall och björk på frisk-fuktig och fuktig mark.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -5260,10 +5265,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122208210</v>
+        <v>122191658</v>
       </c>
       <c r="B38" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5276,44 +5281,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>514264</v>
+        <v>514512</v>
       </c>
       <c r="R38" t="n">
-        <v>7023177</v>
+        <v>7023275</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5351,38 +5349,32 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Med inslag av gran, sälg och björk.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5400,10 +5392,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122208320</v>
+        <v>122208128</v>
       </c>
       <c r="B39" t="n">
-        <v>57399</v>
+        <v>79737</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5416,29 +5408,28 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -5448,13 +5439,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>514264</v>
+        <v>514240</v>
       </c>
       <c r="R39" t="n">
-        <v>7023177</v>
+        <v>7023172</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5488,7 +5479,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Färska hackspår av spillkråka i en sälg.</t>
+          <t>Ymnig påväxt av lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5497,6 +5488,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5520,14 +5512,19 @@
           <t>Salix caprea</t>
         </is>
       </c>
+      <c r="AL39" t="inlineStr">
+        <is>
+          <t>En skadad knäckt men levande sälg.</t>
+        </is>
+      </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Stem on living tree # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea # En skadad knäckt men levande sälg.</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5666,10 +5663,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122193443</v>
+        <v>122207795</v>
       </c>
       <c r="B41" t="n">
-        <v>90857</v>
+        <v>57383</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5682,51 +5679,49 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Sauholmen, Klenflon, Häggenås, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>514671</v>
+        <v>514641</v>
       </c>
       <c r="R41" t="n">
-        <v>7023306</v>
+        <v>7023370</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5758,6 +5753,11 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färska hackspår (ringhack), i basen av en gran, som bedöms vara skapade inom 5 år tillbaks. I området kring denna plats finns även födosökspår på stående smala döda granar.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5769,7 +5769,12 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall och björk på frisk-fuktig och fuktig mark.</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
@@ -5807,10 +5812,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122192869</v>
+        <v>122208320</v>
       </c>
       <c r="B42" t="n">
-        <v>78656</v>
+        <v>57399</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5823,37 +5828,45 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>514655</v>
+        <v>514264</v>
       </c>
       <c r="R42" t="n">
-        <v>7023373</v>
+        <v>7023177</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5885,6 +5898,11 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Färska hackspår av spillkråka i en sälg.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5896,27 +5914,32 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Med inslag av gran, sälg och björk.</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5934,10 +5957,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122208128</v>
+        <v>122192869</v>
       </c>
       <c r="B43" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5950,41 +5973,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>514240</v>
+        <v>514655</v>
       </c>
       <c r="R43" t="n">
-        <v>7023172</v>
+        <v>7023373</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6019,54 +6035,38 @@
           <t>2025-01-18</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ymnig påväxt av lunglav på sälg.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>Med inslag av gran, sälg och björk.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL43" t="inlineStr">
-        <is>
-          <t>En skadad knäckt men levande sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En skadad knäckt men levande sälg.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6084,7 +6084,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122226624</v>
+        <v>122194308</v>
       </c>
       <c r="B44" t="n">
         <v>78656</v>
@@ -6123,17 +6123,17 @@
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>514188</v>
+        <v>514604</v>
       </c>
       <c r="R44" t="n">
-        <v>7023245</v>
+        <v>7023237</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6163,11 +6163,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-01-18</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6187,7 +6182,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Äldre barrskog med en mosaik av talldominerade och grandominerade partier på frisk till fuktig mark.</t>
+          <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -6225,10 +6220,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122194308</v>
+        <v>122194568</v>
       </c>
       <c r="B45" t="n">
-        <v>78656</v>
+        <v>57383</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6241,37 +6236,46 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>514604</v>
+        <v>514580</v>
       </c>
       <c r="R45" t="n">
-        <v>7023237</v>
+        <v>7023243</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6306,13 +6310,17 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på basen av en gran.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6338,12 +6346,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6361,10 +6369,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122194568</v>
+        <v>122226624</v>
       </c>
       <c r="B46" t="n">
-        <v>57383</v>
+        <v>78656</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6377,49 +6385,40 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>514580</v>
+        <v>514188</v>
       </c>
       <c r="R46" t="n">
-        <v>7023243</v>
+        <v>7023245</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6453,7 +6452,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Äldre ringhack på basen av en gran.</t>
+          <t>Garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6462,6 +6461,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
+          <t>Äldre barrskog med en mosaik av talldominerade och grandominerade partier på frisk till fuktig mark.</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6510,10 +6510,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122194394</v>
+        <v>122223793</v>
       </c>
       <c r="B47" t="n">
-        <v>79738</v>
+        <v>79737</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6526,21 +6526,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6553,17 +6553,17 @@
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>514600</v>
+        <v>514631</v>
       </c>
       <c r="R47" t="n">
-        <v>7023243</v>
+        <v>7023229</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>Ett par "knippen" med lunglav på en grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6632,17 +6632,17 @@
       </c>
       <c r="AL47" t="inlineStr">
         <is>
-          <t>En smal skadad knäckt sälg.</t>
+          <t>En något smalare men grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Grov bark. # Salix caprea # En smal skadad knäckt sälg.</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En något smalare men grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6660,10 +6660,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122193783</v>
+        <v>122194394</v>
       </c>
       <c r="B48" t="n">
-        <v>79737</v>
+        <v>79738</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6676,21 +6676,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6703,14 +6703,14 @@
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>514670</v>
+        <v>514600</v>
       </c>
       <c r="R48" t="n">
-        <v>7023247</v>
+        <v>7023243</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6782,7 +6782,7 @@
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>En knäckt smal relativt grovbarkad sälg.</t>
+          <t>En smal skadad knäckt sälg.</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En knäckt smal relativt grovbarkad sälg.</t>
+          <t>Bark of dead wood # Grov bark. # Salix caprea # En smal skadad knäckt sälg.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6810,10 +6810,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122226449</v>
+        <v>122193783</v>
       </c>
       <c r="B49" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6826,40 +6826,44 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514425</v>
+        <v>514670</v>
       </c>
       <c r="R49" t="n">
-        <v>7023228</v>
+        <v>7023247</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6893,7 +6897,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flera granar.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6908,32 +6912,37 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk till fuktig mark. Här finns både stående och liggande död ved. Kolade stubbar indikerar tidigare brandpåverkan.</t>
+          <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL49" t="inlineStr">
+        <is>
+          <t>En knäckt smal relativt grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea # En knäckt smal relativt grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6951,10 +6960,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122223793</v>
+        <v>122226449</v>
       </c>
       <c r="B50" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6967,41 +6976,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sauholmen, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514631</v>
+        <v>514425</v>
       </c>
       <c r="R50" t="n">
-        <v>7023229</v>
+        <v>7023228</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -7038,7 +7043,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ett par "knippen" med lunglav på en grovbarkad sälg.</t>
+          <t>Långväxt garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7053,37 +7058,32 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk till fuktig mark. Här finns både stående och liggande död ved. Kolade stubbar indikerar tidigare brandpåverkan.</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL50" t="inlineStr">
-        <is>
-          <t>En något smalare men grovbarkad sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea # En något smalare men grovbarkad sälg.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>

--- a/artfynd/A 55314-2024 artfynd.xlsx
+++ b/artfynd/A 55314-2024 artfynd.xlsx
@@ -5663,10 +5663,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122207795</v>
+        <v>122208320</v>
       </c>
       <c r="B41" t="n">
-        <v>57383</v>
+        <v>57399</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5679,16 +5679,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5704,21 +5704,17 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sauholmen, Klenflon, Häggenås, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>514641</v>
+        <v>514264</v>
       </c>
       <c r="R41" t="n">
-        <v>7023370</v>
+        <v>7023177</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5755,7 +5751,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Färska hackspår (ringhack), i basen av en gran, som bedöms vara skapade inom 5 år tillbaks. I området kring denna plats finns även födosökspår på stående smala döda granar.</t>
+          <t>Färska hackspår av spillkråka i en sälg.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5769,22 +5765,22 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Grandominerad skog med inslag av tall och björk på frisk-fuktig och fuktig mark.</t>
+          <t>Med inslag av gran, sälg och björk.</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
@@ -5794,7 +5790,7 @@
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5812,10 +5808,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122208320</v>
+        <v>122207795</v>
       </c>
       <c r="B42" t="n">
-        <v>57399</v>
+        <v>57383</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5828,16 +5824,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5853,17 +5849,21 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Sauholmen, Klenflon, Häggenås, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>514264</v>
+        <v>514641</v>
       </c>
       <c r="R42" t="n">
-        <v>7023177</v>
+        <v>7023370</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Färska hackspår av spillkråka i en sälg.</t>
+          <t>Färska hackspår (ringhack), i basen av en gran, som bedöms vara skapade inom 5 år tillbaks. I området kring denna plats finns även födosökspår på stående smala döda granar.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5914,22 +5914,22 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Med inslag av gran, sälg och björk.</t>
+          <t>Grandominerad skog med inslag av tall och björk på frisk-fuktig och fuktig mark.</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Stem on living tree # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>

--- a/artfynd/A 55314-2024 artfynd.xlsx
+++ b/artfynd/A 55314-2024 artfynd.xlsx
@@ -6220,10 +6220,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122194568</v>
+        <v>122194394</v>
       </c>
       <c r="B45" t="n">
-        <v>57383</v>
+        <v>79738</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6236,43 +6236,38 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>514580</v>
+        <v>514600</v>
       </c>
       <c r="R45" t="n">
         <v>7023243</v>
@@ -6312,7 +6307,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Äldre ringhack på basen av en gran.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6321,6 +6316,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6336,22 +6332,27 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL45" t="inlineStr">
+        <is>
+          <t>En smal skadad knäckt sälg.</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark of dead wood # Grov bark. # Salix caprea # En smal skadad knäckt sälg.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6369,10 +6370,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122226624</v>
+        <v>122223793</v>
       </c>
       <c r="B46" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6385,37 +6386,41 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>514188</v>
+        <v>514631</v>
       </c>
       <c r="R46" t="n">
-        <v>7023245</v>
+        <v>7023229</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -6452,7 +6457,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Garnlav på flera granar.</t>
+          <t>Ett par "knippen" med lunglav på en grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6472,27 +6477,32 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Äldre barrskog med en mosaik av talldominerade och grandominerade partier på frisk till fuktig mark.</t>
+          <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL46" t="inlineStr">
+        <is>
+          <t>En något smalare men grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En något smalare men grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6510,10 +6520,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122223793</v>
+        <v>122194568</v>
       </c>
       <c r="B47" t="n">
-        <v>79737</v>
+        <v>57383</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6526,44 +6536,49 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sauholmen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>514631</v>
+        <v>514580</v>
       </c>
       <c r="R47" t="n">
-        <v>7023229</v>
+        <v>7023243</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6597,7 +6612,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ett par "knippen" med lunglav på en grovbarkad sälg.</t>
+          <t>Äldre ringhack på basen av en gran.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6606,7 +6621,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6622,27 +6636,22 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL47" t="inlineStr">
-        <is>
-          <t>En något smalare men grovbarkad sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea # En något smalare men grovbarkad sälg.</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6660,10 +6669,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122194394</v>
+        <v>122226624</v>
       </c>
       <c r="B48" t="n">
-        <v>79738</v>
+        <v>78656</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6676,44 +6685,40 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>514600</v>
+        <v>514188</v>
       </c>
       <c r="R48" t="n">
-        <v>7023243</v>
+        <v>7023245</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6747,7 +6752,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>Garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6767,32 +6772,27 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
+          <t>Äldre barrskog med en mosaik av talldominerade och grandominerade partier på frisk till fuktig mark.</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL48" t="inlineStr">
-        <is>
-          <t>En smal skadad knäckt sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Grov bark. # Salix caprea # En smal skadad knäckt sälg.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6810,10 +6810,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122193783</v>
+        <v>122226449</v>
       </c>
       <c r="B49" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6826,44 +6826,40 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514670</v>
+        <v>514425</v>
       </c>
       <c r="R49" t="n">
-        <v>7023247</v>
+        <v>7023228</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6897,7 +6893,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>Långväxt garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6912,37 +6908,32 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk till fuktig mark. Här finns både stående och liggande död ved. Kolade stubbar indikerar tidigare brandpåverkan.</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL49" t="inlineStr">
-        <is>
-          <t>En knäckt smal relativt grovbarkad sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En knäckt smal relativt grovbarkad sälg.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6960,10 +6951,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122226449</v>
+        <v>122193783</v>
       </c>
       <c r="B50" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6976,40 +6967,44 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514425</v>
+        <v>514670</v>
       </c>
       <c r="R50" t="n">
-        <v>7023228</v>
+        <v>7023247</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7043,7 +7038,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flera granar.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7058,32 +7053,37 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk till fuktig mark. Här finns både stående och liggande död ved. Kolade stubbar indikerar tidigare brandpåverkan.</t>
+          <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL50" t="inlineStr">
+        <is>
+          <t>En knäckt smal relativt grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea # En knäckt smal relativt grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>

--- a/artfynd/A 55314-2024 artfynd.xlsx
+++ b/artfynd/A 55314-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AY56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7253,6 +7253,581 @@
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>122663511</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79738</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Sauholmen, Sauholmen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>514749</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7023284</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>122667349</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79738</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Lillberget, Lillberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>514253</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7023302</v>
+      </c>
+      <c r="S53" t="n">
+        <v>7</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>122662339</v>
+      </c>
+      <c r="B54" t="n">
+        <v>78657</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Lillberget, Lillberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>514345</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7023366</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>122662245</v>
+      </c>
+      <c r="B55" t="n">
+        <v>78657</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Lillberget, Lillberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>514347</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7023344</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>122662456</v>
+      </c>
+      <c r="B56" t="n">
+        <v>56594</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Lillberget, Klenflon, Häggenås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>514349</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7023392</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55314-2024 artfynd.xlsx
+++ b/artfynd/A 55314-2024 artfynd.xlsx
@@ -7104,7 +7104,7 @@
         <v>122223410</v>
       </c>
       <c r="B51" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7387,10 +7387,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122667349</v>
+        <v>122662245</v>
       </c>
       <c r="B53" t="n">
-        <v>79738</v>
+        <v>78657</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7403,42 +7403,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>514253</v>
+        <v>514347</v>
       </c>
       <c r="R53" t="n">
-        <v>7023302</v>
+        <v>7023344</v>
       </c>
       <c r="S53" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7478,31 +7473,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -7519,10 +7489,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122662339</v>
+        <v>122662456</v>
       </c>
       <c r="B54" t="n">
-        <v>78657</v>
+        <v>56594</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7531,38 +7501,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Lillberget, Klenflon, Häggenås, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>514345</v>
+        <v>514349</v>
       </c>
       <c r="R54" t="n">
-        <v>7023366</v>
+        <v>7023392</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7621,10 +7596,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122662245</v>
+        <v>122667349</v>
       </c>
       <c r="B55" t="n">
-        <v>78657</v>
+        <v>79738</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7637,37 +7612,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>514347</v>
+        <v>514253</v>
       </c>
       <c r="R55" t="n">
-        <v>7023344</v>
+        <v>7023302</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7707,6 +7687,31 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7723,10 +7728,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122662456</v>
+        <v>122662339</v>
       </c>
       <c r="B56" t="n">
-        <v>56594</v>
+        <v>78657</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7735,43 +7740,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lillberget, Klenflon, Häggenås, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>514349</v>
+        <v>514345</v>
       </c>
       <c r="R56" t="n">
-        <v>7023392</v>
+        <v>7023366</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>

--- a/artfynd/A 55314-2024 artfynd.xlsx
+++ b/artfynd/A 55314-2024 artfynd.xlsx
@@ -7255,10 +7255,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122663511</v>
+        <v>122662245</v>
       </c>
       <c r="B52" t="n">
-        <v>79738</v>
+        <v>78657</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7271,39 +7271,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>514749</v>
+        <v>514347</v>
       </c>
       <c r="R52" t="n">
-        <v>7023284</v>
+        <v>7023344</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7346,31 +7341,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -7387,10 +7357,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122662245</v>
+        <v>122663511</v>
       </c>
       <c r="B53" t="n">
-        <v>78657</v>
+        <v>79738</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7403,34 +7373,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>514347</v>
+        <v>514749</v>
       </c>
       <c r="R53" t="n">
-        <v>7023344</v>
+        <v>7023284</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7473,6 +7448,31 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">

--- a/artfynd/A 55314-2024 artfynd.xlsx
+++ b/artfynd/A 55314-2024 artfynd.xlsx
@@ -7255,10 +7255,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122662245</v>
+        <v>122663511</v>
       </c>
       <c r="B52" t="n">
-        <v>78657</v>
+        <v>79741</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7271,34 +7271,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>514347</v>
+        <v>514749</v>
       </c>
       <c r="R52" t="n">
-        <v>7023344</v>
+        <v>7023284</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7341,6 +7346,31 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -7357,10 +7387,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122663511</v>
+        <v>122662456</v>
       </c>
       <c r="B53" t="n">
-        <v>79738</v>
+        <v>56594</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7369,43 +7399,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Klenflon, Häggenås, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>514749</v>
+        <v>514349</v>
       </c>
       <c r="R53" t="n">
-        <v>7023284</v>
+        <v>7023392</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7448,31 +7478,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -7489,10 +7494,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122662456</v>
+        <v>122662339</v>
       </c>
       <c r="B54" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7501,43 +7506,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lillberget, Klenflon, Häggenås, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>514349</v>
+        <v>514345</v>
       </c>
       <c r="R54" t="n">
-        <v>7023392</v>
+        <v>7023366</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7599,7 +7599,7 @@
         <v>122667349</v>
       </c>
       <c r="B55" t="n">
-        <v>79738</v>
+        <v>79741</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7728,10 +7728,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122662339</v>
+        <v>122662245</v>
       </c>
       <c r="B56" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7768,10 +7768,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>514345</v>
+        <v>514347</v>
       </c>
       <c r="R56" t="n">
-        <v>7023366</v>
+        <v>7023344</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>

--- a/artfynd/A 55314-2024 artfynd.xlsx
+++ b/artfynd/A 55314-2024 artfynd.xlsx
@@ -7255,10 +7255,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122663511</v>
+        <v>122662456</v>
       </c>
       <c r="B52" t="n">
-        <v>79741</v>
+        <v>56594</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7267,43 +7267,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Klenflon, Häggenås, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>514749</v>
+        <v>514349</v>
       </c>
       <c r="R52" t="n">
-        <v>7023284</v>
+        <v>7023392</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7346,31 +7346,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -7387,10 +7362,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122662456</v>
+        <v>122662245</v>
       </c>
       <c r="B53" t="n">
-        <v>56594</v>
+        <v>78660</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7399,43 +7374,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lillberget, Klenflon, Häggenås, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>514349</v>
+        <v>514347</v>
       </c>
       <c r="R53" t="n">
-        <v>7023392</v>
+        <v>7023344</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7494,10 +7464,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122662339</v>
+        <v>122663511</v>
       </c>
       <c r="B54" t="n">
-        <v>78660</v>
+        <v>79741</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7510,34 +7480,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>514345</v>
+        <v>514749</v>
       </c>
       <c r="R54" t="n">
-        <v>7023366</v>
+        <v>7023284</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7580,6 +7555,31 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -7728,7 +7728,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122662245</v>
+        <v>122662339</v>
       </c>
       <c r="B56" t="n">
         <v>78660</v>
@@ -7768,10 +7768,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>514347</v>
+        <v>514345</v>
       </c>
       <c r="R56" t="n">
-        <v>7023344</v>
+        <v>7023366</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>

--- a/artfynd/A 55314-2024 artfynd.xlsx
+++ b/artfynd/A 55314-2024 artfynd.xlsx
@@ -7255,10 +7255,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122662245</v>
+        <v>122662339</v>
       </c>
       <c r="B52" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7295,10 +7295,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>514347</v>
+        <v>514345</v>
       </c>
       <c r="R52" t="n">
-        <v>7023344</v>
+        <v>7023366</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7357,10 +7357,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122667349</v>
+        <v>122663511</v>
       </c>
       <c r="B53" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7398,17 +7398,17 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>514253</v>
+        <v>514749</v>
       </c>
       <c r="R53" t="n">
-        <v>7023302</v>
+        <v>7023284</v>
       </c>
       <c r="S53" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7466,12 +7466,12 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7489,10 +7489,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122662339</v>
+        <v>122662456</v>
       </c>
       <c r="B54" t="n">
-        <v>78762</v>
+        <v>56688</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7501,38 +7501,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Lillberget, Klenflon, Häggenås, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>514345</v>
+        <v>514349</v>
       </c>
       <c r="R54" t="n">
-        <v>7023366</v>
+        <v>7023392</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7591,10 +7596,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122663511</v>
+        <v>122667349</v>
       </c>
       <c r="B55" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7632,17 +7637,17 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>514749</v>
+        <v>514253</v>
       </c>
       <c r="R55" t="n">
-        <v>7023284</v>
+        <v>7023302</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7700,12 +7705,12 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7723,10 +7728,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122662456</v>
+        <v>122662245</v>
       </c>
       <c r="B56" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7735,43 +7740,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lillberget, Klenflon, Häggenås, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>514349</v>
+        <v>514347</v>
       </c>
       <c r="R56" t="n">
-        <v>7023392</v>
+        <v>7023344</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>

--- a/artfynd/A 55314-2024 artfynd.xlsx
+++ b/artfynd/A 55314-2024 artfynd.xlsx
@@ -7357,10 +7357,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122663511</v>
+        <v>122662456</v>
       </c>
       <c r="B53" t="n">
-        <v>79847</v>
+        <v>56688</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7369,43 +7369,43 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Klenflon, Häggenås, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>514749</v>
+        <v>514349</v>
       </c>
       <c r="R53" t="n">
-        <v>7023284</v>
+        <v>7023392</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7448,31 +7448,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -7489,10 +7464,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122662456</v>
+        <v>122662245</v>
       </c>
       <c r="B54" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7501,43 +7476,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lillberget, Klenflon, Häggenås, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>514349</v>
+        <v>514347</v>
       </c>
       <c r="R54" t="n">
-        <v>7023392</v>
+        <v>7023344</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7596,7 +7566,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122667349</v>
+        <v>122663511</v>
       </c>
       <c r="B55" t="n">
         <v>79847</v>
@@ -7637,17 +7607,17 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>514253</v>
+        <v>514749</v>
       </c>
       <c r="R55" t="n">
-        <v>7023302</v>
+        <v>7023284</v>
       </c>
       <c r="S55" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7705,12 +7675,12 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7728,10 +7698,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122662245</v>
+        <v>122667349</v>
       </c>
       <c r="B56" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7744,37 +7714,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>514347</v>
+        <v>514253</v>
       </c>
       <c r="R56" t="n">
-        <v>7023344</v>
+        <v>7023302</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7814,6 +7789,31 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">

--- a/artfynd/A 55314-2024 artfynd.xlsx
+++ b/artfynd/A 55314-2024 artfynd.xlsx
@@ -7255,10 +7255,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122662339</v>
+        <v>122667349</v>
       </c>
       <c r="B52" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7271,37 +7271,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>514345</v>
+        <v>514253</v>
       </c>
       <c r="R52" t="n">
-        <v>7023366</v>
+        <v>7023302</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7341,6 +7346,31 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -7357,10 +7387,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122662456</v>
+        <v>122662245</v>
       </c>
       <c r="B53" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7369,43 +7399,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lillberget, Klenflon, Häggenås, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>514349</v>
+        <v>514347</v>
       </c>
       <c r="R53" t="n">
-        <v>7023392</v>
+        <v>7023344</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7464,10 +7489,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122662245</v>
+        <v>122662456</v>
       </c>
       <c r="B54" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7476,38 +7501,43 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Lillberget, Klenflon, Häggenås, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>514347</v>
+        <v>514349</v>
       </c>
       <c r="R54" t="n">
-        <v>7023344</v>
+        <v>7023392</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7566,10 +7596,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122663511</v>
+        <v>122662339</v>
       </c>
       <c r="B55" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7582,39 +7612,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>514749</v>
+        <v>514345</v>
       </c>
       <c r="R55" t="n">
-        <v>7023284</v>
+        <v>7023366</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7657,31 +7682,6 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7698,7 +7698,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122667349</v>
+        <v>122663511</v>
       </c>
       <c r="B56" t="n">
         <v>79847</v>
@@ -7739,17 +7739,17 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>514253</v>
+        <v>514749</v>
       </c>
       <c r="R56" t="n">
-        <v>7023302</v>
+        <v>7023284</v>
       </c>
       <c r="S56" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>

--- a/artfynd/A 55314-2024 artfynd.xlsx
+++ b/artfynd/A 55314-2024 artfynd.xlsx
@@ -7255,10 +7255,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122667349</v>
+        <v>122662456</v>
       </c>
       <c r="B52" t="n">
-        <v>79847</v>
+        <v>56688</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7267,46 +7267,46 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Lillberget, Klenflon, Häggenås, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>514253</v>
+        <v>514349</v>
       </c>
       <c r="R52" t="n">
-        <v>7023302</v>
+        <v>7023392</v>
       </c>
       <c r="S52" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7346,31 +7346,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -7387,7 +7362,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122662245</v>
+        <v>122662339</v>
       </c>
       <c r="B53" t="n">
         <v>78766</v>
@@ -7427,10 +7402,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>514347</v>
+        <v>514345</v>
       </c>
       <c r="R53" t="n">
-        <v>7023344</v>
+        <v>7023366</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7489,10 +7464,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122662456</v>
+        <v>122667349</v>
       </c>
       <c r="B54" t="n">
-        <v>56688</v>
+        <v>79847</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7501,46 +7476,46 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>hona</t>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lillberget, Klenflon, Häggenås, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>514349</v>
+        <v>514253</v>
       </c>
       <c r="R54" t="n">
-        <v>7023392</v>
+        <v>7023302</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7580,6 +7555,31 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -7596,10 +7596,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122662339</v>
+        <v>122663511</v>
       </c>
       <c r="B55" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7612,34 +7612,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>514345</v>
+        <v>514749</v>
       </c>
       <c r="R55" t="n">
-        <v>7023366</v>
+        <v>7023284</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7682,6 +7687,31 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7698,10 +7728,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122663511</v>
+        <v>122662245</v>
       </c>
       <c r="B56" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7714,39 +7744,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>514749</v>
+        <v>514347</v>
       </c>
       <c r="R56" t="n">
-        <v>7023284</v>
+        <v>7023344</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7789,31 +7814,6 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">

--- a/artfynd/A 55314-2024 artfynd.xlsx
+++ b/artfynd/A 55314-2024 artfynd.xlsx
@@ -7362,10 +7362,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122662339</v>
+        <v>122667349</v>
       </c>
       <c r="B53" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7378,37 +7378,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>514345</v>
+        <v>514253</v>
       </c>
       <c r="R53" t="n">
-        <v>7023366</v>
+        <v>7023302</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7448,6 +7453,31 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -7464,10 +7494,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122667349</v>
+        <v>122662245</v>
       </c>
       <c r="B54" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7480,42 +7510,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>514253</v>
+        <v>514347</v>
       </c>
       <c r="R54" t="n">
-        <v>7023302</v>
+        <v>7023344</v>
       </c>
       <c r="S54" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7555,31 +7580,6 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -7596,10 +7596,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122663511</v>
+        <v>122662339</v>
       </c>
       <c r="B55" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7612,39 +7612,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>514749</v>
+        <v>514345</v>
       </c>
       <c r="R55" t="n">
-        <v>7023284</v>
+        <v>7023366</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7687,31 +7682,6 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7728,10 +7698,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122662245</v>
+        <v>122663511</v>
       </c>
       <c r="B56" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7744,34 +7714,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>514347</v>
+        <v>514749</v>
       </c>
       <c r="R56" t="n">
-        <v>7023344</v>
+        <v>7023284</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7814,6 +7789,31 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">

--- a/artfynd/A 55314-2024 artfynd.xlsx
+++ b/artfynd/A 55314-2024 artfynd.xlsx
@@ -7255,10 +7255,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122662456</v>
+        <v>122667349</v>
       </c>
       <c r="B52" t="n">
-        <v>56688</v>
+        <v>79847</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7267,46 +7267,46 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>hona</t>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lillberget, Klenflon, Häggenås, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>514349</v>
+        <v>514253</v>
       </c>
       <c r="R52" t="n">
-        <v>7023392</v>
+        <v>7023302</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7346,6 +7346,31 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -7362,10 +7387,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122667349</v>
+        <v>122662456</v>
       </c>
       <c r="B53" t="n">
-        <v>79847</v>
+        <v>56688</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7374,46 +7399,46 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Lillberget, Klenflon, Häggenås, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>514253</v>
+        <v>514349</v>
       </c>
       <c r="R53" t="n">
-        <v>7023302</v>
+        <v>7023392</v>
       </c>
       <c r="S53" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7453,31 +7478,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">

--- a/artfynd/A 55314-2024 artfynd.xlsx
+++ b/artfynd/A 55314-2024 artfynd.xlsx
@@ -7255,10 +7255,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122667349</v>
+        <v>122662456</v>
       </c>
       <c r="B52" t="n">
-        <v>79847</v>
+        <v>56688</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7267,46 +7267,46 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Lillberget, Klenflon, Häggenås, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>514253</v>
+        <v>514349</v>
       </c>
       <c r="R52" t="n">
-        <v>7023302</v>
+        <v>7023392</v>
       </c>
       <c r="S52" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7346,31 +7346,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -7387,10 +7362,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122662456</v>
+        <v>122662339</v>
       </c>
       <c r="B53" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7399,43 +7374,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lillberget, Klenflon, Häggenås, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>514349</v>
+        <v>514345</v>
       </c>
       <c r="R53" t="n">
-        <v>7023392</v>
+        <v>7023366</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7596,10 +7566,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122662339</v>
+        <v>122667349</v>
       </c>
       <c r="B55" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7612,37 +7582,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>514345</v>
+        <v>514253</v>
       </c>
       <c r="R55" t="n">
-        <v>7023366</v>
+        <v>7023302</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7682,6 +7657,31 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">

--- a/artfynd/A 55314-2024 artfynd.xlsx
+++ b/artfynd/A 55314-2024 artfynd.xlsx
@@ -7255,10 +7255,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122662456</v>
+        <v>122667349</v>
       </c>
       <c r="B52" t="n">
-        <v>56688</v>
+        <v>79847</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7267,46 +7267,46 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>hona</t>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lillberget, Klenflon, Häggenås, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>514349</v>
+        <v>514253</v>
       </c>
       <c r="R52" t="n">
-        <v>7023392</v>
+        <v>7023302</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7346,6 +7346,31 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -7464,10 +7489,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122662245</v>
+        <v>122663511</v>
       </c>
       <c r="B54" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7480,34 +7505,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>514347</v>
+        <v>514749</v>
       </c>
       <c r="R54" t="n">
-        <v>7023344</v>
+        <v>7023284</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7550,6 +7580,31 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -7566,10 +7621,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122667349</v>
+        <v>122662456</v>
       </c>
       <c r="B55" t="n">
-        <v>79847</v>
+        <v>56688</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7578,46 +7633,46 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Lillberget, Klenflon, Häggenås, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>514253</v>
+        <v>514349</v>
       </c>
       <c r="R55" t="n">
-        <v>7023302</v>
+        <v>7023392</v>
       </c>
       <c r="S55" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7657,31 +7712,6 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7698,10 +7728,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122663511</v>
+        <v>122662245</v>
       </c>
       <c r="B56" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7714,39 +7744,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>514749</v>
+        <v>514347</v>
       </c>
       <c r="R56" t="n">
-        <v>7023284</v>
+        <v>7023344</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7789,31 +7814,6 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">

--- a/artfynd/A 55314-2024 artfynd.xlsx
+++ b/artfynd/A 55314-2024 artfynd.xlsx
@@ -7255,10 +7255,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122667349</v>
+        <v>122662456</v>
       </c>
       <c r="B52" t="n">
-        <v>79847</v>
+        <v>56688</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7267,46 +7267,46 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Lillberget, Klenflon, Häggenås, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>514253</v>
+        <v>514349</v>
       </c>
       <c r="R52" t="n">
-        <v>7023302</v>
+        <v>7023392</v>
       </c>
       <c r="S52" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7346,31 +7346,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -7387,10 +7362,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122662339</v>
+        <v>122667349</v>
       </c>
       <c r="B53" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7403,37 +7378,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>514345</v>
+        <v>514253</v>
       </c>
       <c r="R53" t="n">
-        <v>7023366</v>
+        <v>7023302</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7473,6 +7453,31 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -7621,10 +7626,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122662456</v>
+        <v>122662245</v>
       </c>
       <c r="B55" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7633,43 +7638,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lillberget, Klenflon, Häggenås, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>514349</v>
+        <v>514347</v>
       </c>
       <c r="R55" t="n">
-        <v>7023392</v>
+        <v>7023344</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7728,7 +7728,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122662245</v>
+        <v>122662339</v>
       </c>
       <c r="B56" t="n">
         <v>78766</v>
@@ -7768,10 +7768,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>514347</v>
+        <v>514345</v>
       </c>
       <c r="R56" t="n">
-        <v>7023344</v>
+        <v>7023366</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>

--- a/artfynd/A 55314-2024 artfynd.xlsx
+++ b/artfynd/A 55314-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AY55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121668309</v>
+        <v>121667142</v>
       </c>
       <c r="B2" t="n">
-        <v>78632</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514672</v>
+        <v>514636</v>
       </c>
       <c r="R2" t="n">
-        <v>7023245</v>
+        <v>7023234</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,12 +755,18 @@
           <t>2024-12-19</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Gott om bålar av både skrovellav och lunglav på en sälg.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -767,24 +775,34 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
+        </is>
+      </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>En gammal tvåstammig delvis skadad sälg.</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En gammal tvåstammig delvis skadad sälg.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,15 +820,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121667141</v>
+        <v>121670773</v>
       </c>
       <c r="B3" t="n">
-        <v>79737</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,41 +831,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514636</v>
+        <v>514216</v>
       </c>
       <c r="R3" t="n">
-        <v>7023234</v>
+        <v>7023241</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,55 +893,14 @@
           <t>2024-12-19</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ymnig påväxt av lunglav på en gammal sälg där det även växer skrovellav, luddlav etc.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>En gammal tvåstammig delvis skadad sälg.</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea # En gammal tvåstammig delvis skadad sälg.</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -952,15 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121668931</v>
+        <v>121670797</v>
       </c>
       <c r="B4" t="n">
-        <v>78632</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -968,34 +928,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514674</v>
+        <v>514262</v>
       </c>
       <c r="R4" t="n">
-        <v>7023130</v>
+        <v>7023275</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1041,27 +1006,27 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1079,15 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121669062</v>
+        <v>121671169</v>
       </c>
       <c r="B5" t="n">
-        <v>57383</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,42 +1055,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514434</v>
+        <v>514228</v>
       </c>
       <c r="R5" t="n">
-        <v>7023257</v>
+        <v>7023328</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1165,11 +1117,6 @@
           <t>2024-12-19</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1178,36 +1125,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk till fuktig mark. Här finns både stående och liggande död ved.</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1224,15 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121667545</v>
+        <v>122194394</v>
       </c>
       <c r="B6" t="n">
-        <v>78632</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,34 +1152,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514742</v>
+        <v>514600</v>
       </c>
       <c r="R6" t="n">
-        <v>7023172</v>
+        <v>7023243</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1294,12 +1213,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2025-01-18</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1308,6 +1232,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1316,24 +1241,34 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
+        </is>
+      </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>En smal skadad knäckt sälg.</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Grov bark. # Salix caprea # En smal skadad knäckt sälg.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1351,50 +1286,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121670504</v>
+        <v>121666824</v>
       </c>
       <c r="B7" t="n">
-        <v>79713</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514335</v>
+        <v>514678</v>
       </c>
       <c r="R7" t="n">
-        <v>7023306</v>
+        <v>7023186</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1437,6 +1367,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1453,50 +1408,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121670773</v>
+        <v>121666863</v>
       </c>
       <c r="B8" t="n">
-        <v>79714</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514216</v>
+        <v>514695</v>
       </c>
       <c r="R8" t="n">
-        <v>7023241</v>
+        <v>7023177</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1539,6 +1489,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1555,55 +1530,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121670797</v>
+        <v>121667138</v>
       </c>
       <c r="B9" t="n">
-        <v>79714</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514262</v>
+        <v>514735</v>
       </c>
       <c r="R9" t="n">
-        <v>7023275</v>
+        <v>7023174</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1649,27 +1614,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1687,19 +1652,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121671163</v>
+        <v>121667545</v>
       </c>
       <c r="B10" t="n">
-        <v>78632</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1723,14 +1683,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514227</v>
+        <v>514742</v>
       </c>
       <c r="R10" t="n">
-        <v>7023300</v>
+        <v>7023172</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1814,57 +1774,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121667143</v>
+        <v>121668309</v>
       </c>
       <c r="B11" t="n">
-        <v>79766</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514636</v>
+        <v>514672</v>
       </c>
       <c r="R11" t="n">
-        <v>7023234</v>
+        <v>7023245</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1905,7 +1853,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1914,29 +1861,24 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
-        </is>
-      </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1954,19 +1896,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121666863</v>
+        <v>121668931</v>
       </c>
       <c r="B12" t="n">
-        <v>78632</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1994,10 +1931,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514695</v>
+        <v>514674</v>
       </c>
       <c r="R12" t="n">
-        <v>7023177</v>
+        <v>7023130</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2081,60 +2018,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121666620</v>
+        <v>121669034</v>
       </c>
       <c r="B13" t="n">
-        <v>57381</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514538</v>
+        <v>514722</v>
       </c>
       <c r="R13" t="n">
-        <v>7023126</v>
+        <v>7023113</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2180,7 +2102,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Våtmark med barrträd</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2195,12 +2117,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2218,55 +2140,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121670799</v>
+        <v>121669094</v>
       </c>
       <c r="B14" t="n">
-        <v>79742</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514265</v>
+        <v>514711</v>
       </c>
       <c r="R14" t="n">
-        <v>7023278</v>
+        <v>7023153</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2312,27 +2224,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Våtmark med barrträd</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2350,37 +2262,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121671169</v>
+        <v>121671163</v>
       </c>
       <c r="B15" t="n">
-        <v>79714</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2390,10 +2297,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514228</v>
+        <v>514227</v>
       </c>
       <c r="R15" t="n">
-        <v>7023328</v>
+        <v>7023300</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2436,6 +2343,31 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2452,55 +2384,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121671072</v>
+        <v>122191658</v>
       </c>
       <c r="B16" t="n">
-        <v>57365</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514232</v>
+        <v>514512</v>
       </c>
       <c r="R16" t="n">
-        <v>7023294</v>
+        <v>7023275</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2527,12 +2449,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2543,6 +2465,31 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2559,19 +2506,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121669034</v>
+        <v>122192869</v>
       </c>
       <c r="B17" t="n">
-        <v>78632</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2599,10 +2541,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514722</v>
+        <v>514655</v>
       </c>
       <c r="R17" t="n">
-        <v>7023113</v>
+        <v>7023373</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2629,12 +2571,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2648,7 +2590,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Våtmark med barrträd</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2686,50 +2628,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121667649</v>
+        <v>122194308</v>
       </c>
       <c r="B18" t="n">
-        <v>79713</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514709</v>
+        <v>514604</v>
       </c>
       <c r="R18" t="n">
-        <v>7023250</v>
+        <v>7023237</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2756,12 +2696,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2770,8 +2710,39 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2788,58 +2759,51 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121671097</v>
+        <v>122226449</v>
       </c>
       <c r="B19" t="n">
-        <v>79713</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514216</v>
+        <v>514425</v>
       </c>
       <c r="R19" t="n">
-        <v>7023328</v>
+        <v>7023228</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2863,12 +2827,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2025-01-18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Långväxt garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2877,32 +2846,38 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk till fuktig mark. Här finns både stående och liggande död ved. Kolade stubbar indikerar tidigare brandpåverkan.</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2920,53 +2895,51 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121671167</v>
+        <v>122226624</v>
       </c>
       <c r="B20" t="n">
-        <v>79713</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514229</v>
+        <v>514188</v>
       </c>
       <c r="R20" t="n">
-        <v>7023329</v>
+        <v>7023245</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2990,12 +2963,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2025-01-18</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3004,8 +2982,39 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Äldre barrskog med en mosaik av talldominerade och grandominerade partier på frisk till fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3022,37 +3031,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121670772</v>
+        <v>122662245</v>
       </c>
       <c r="B21" t="n">
-        <v>79713</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3062,10 +3066,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514217</v>
+        <v>514347</v>
       </c>
       <c r="R21" t="n">
-        <v>7023244</v>
+        <v>7023344</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3092,12 +3096,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3124,58 +3128,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121669887</v>
+        <v>122662339</v>
       </c>
       <c r="B22" t="n">
-        <v>57383</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514428</v>
+        <v>514345</v>
       </c>
       <c r="R22" t="n">
-        <v>7023241</v>
+        <v>7023366</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3202,17 +3193,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3223,36 +3209,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk till fuktig mark. Här finns både stående och liggande död ved.</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3269,19 +3225,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121669094</v>
+        <v>122663546</v>
       </c>
       <c r="B23" t="n">
-        <v>78632</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3309,10 +3260,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514711</v>
+        <v>514759</v>
       </c>
       <c r="R23" t="n">
-        <v>7023153</v>
+        <v>7023277</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3339,12 +3290,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3358,7 +3309,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Våtmark med barrträd</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -3396,15 +3347,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121671149</v>
+        <v>121667141</v>
       </c>
       <c r="B24" t="n">
-        <v>79713</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3430,16 +3376,23 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>514237</v>
+        <v>514636</v>
       </c>
       <c r="R24" t="n">
-        <v>7023316</v>
+        <v>7023234</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3474,14 +3427,55 @@
           <t>2024-12-19</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ymnig påväxt av lunglav på en gammal sälg där det även växer skrovellav, luddlav etc.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>En gammal tvåstammig delvis skadad sälg.</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En gammal tvåstammig delvis skadad sälg.</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3498,15 +3492,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121671125</v>
+        <v>121667649</v>
       </c>
       <c r="B25" t="n">
-        <v>79713</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3532,21 +3521,16 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>514222</v>
+        <v>514709</v>
       </c>
       <c r="R25" t="n">
-        <v>7023316</v>
+        <v>7023250</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3589,31 +3573,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3630,15 +3589,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121670532</v>
+        <v>121670504</v>
       </c>
       <c r="B26" t="n">
-        <v>90763</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3646,48 +3600,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>514314</v>
+        <v>514335</v>
       </c>
       <c r="R26" t="n">
-        <v>7023286</v>
+        <v>7023306</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3730,31 +3670,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3771,15 +3686,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121667138</v>
+        <v>121670575</v>
       </c>
       <c r="B27" t="n">
-        <v>78632</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3787,34 +3697,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>514735</v>
+        <v>514301</v>
       </c>
       <c r="R27" t="n">
-        <v>7023174</v>
+        <v>7023286</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3857,31 +3767,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3898,15 +3783,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121666824</v>
+        <v>121670753</v>
       </c>
       <c r="B28" t="n">
-        <v>78632</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3914,34 +3794,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>514678</v>
+        <v>514257</v>
       </c>
       <c r="R28" t="n">
-        <v>7023186</v>
+        <v>7023271</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3987,27 +3867,27 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4025,53 +3905,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121667163</v>
+        <v>121670772</v>
       </c>
       <c r="B29" t="n">
-        <v>79772</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>514636</v>
+        <v>514217</v>
       </c>
       <c r="R29" t="n">
-        <v>7023234</v>
+        <v>7023244</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4112,39 +3984,8 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4161,15 +4002,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121669055</v>
+        <v>121671097</v>
       </c>
       <c r="B30" t="n">
-        <v>57383</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4177,42 +4013,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514434</v>
+        <v>514216</v>
       </c>
       <c r="R30" t="n">
-        <v>7023259</v>
+        <v>7023328</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4247,11 +4080,6 @@
           <t>2024-12-19</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4263,32 +4091,27 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk till fuktig mark. Här finns både stående och liggande död ved.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4306,15 +4129,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121670753</v>
+        <v>121671125</v>
       </c>
       <c r="B31" t="n">
-        <v>79713</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4340,16 +4158,21 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>514257</v>
+        <v>514222</v>
       </c>
       <c r="R31" t="n">
-        <v>7023271</v>
+        <v>7023316</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4395,7 +4218,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -4433,57 +4256,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121667243</v>
+        <v>121671149</v>
       </c>
       <c r="B32" t="n">
-        <v>79773</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514636</v>
+        <v>514237</v>
       </c>
       <c r="R32" t="n">
-        <v>7023234</v>
+        <v>7023316</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4518,55 +4329,14 @@
           <t>2024-12-19</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>En gammal tvåstammig delvis skadad sälg.</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea # En gammal tvåstammig delvis skadad sälg.</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4583,15 +4353,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121670575</v>
+        <v>121671167</v>
       </c>
       <c r="B33" t="n">
-        <v>79713</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4623,10 +4388,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>514301</v>
+        <v>514229</v>
       </c>
       <c r="R33" t="n">
-        <v>7023286</v>
+        <v>7023329</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4685,15 +4450,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121667142</v>
+        <v>122193783</v>
       </c>
       <c r="B34" t="n">
-        <v>79738</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4701,21 +4461,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4732,10 +4492,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514636</v>
+        <v>514670</v>
       </c>
       <c r="R34" t="n">
-        <v>7023234</v>
+        <v>7023247</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4762,17 +4522,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Gott om bålar av både skrovellav och lunglav på en sälg.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4807,17 +4567,17 @@
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>En gammal tvåstammig delvis skadad sälg.</t>
+          <t>En knäckt smal relativt grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea # En gammal tvåstammig delvis skadad sälg.</t>
+          <t>Bark of dead wood # Salix caprea # En knäckt smal relativt grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4835,15 +4595,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122208029</v>
+        <v>122208128</v>
       </c>
       <c r="B35" t="n">
-        <v>57399</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4851,49 +4606,44 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lillberget, Klenflon, Häggenås, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514232</v>
+        <v>514240</v>
       </c>
       <c r="R35" t="n">
-        <v>7023309</v>
+        <v>7023172</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4927,7 +4677,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Färska rejäla hackspår av spillkråka i basen av en gran.</t>
+          <t>Ymnig påväxt av lunglav på sälg.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4936,37 +4686,43 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Äldre skog med olikåldriga träd.</t>
+          <t>Med inslag av gran, sälg och björk.</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL35" t="inlineStr">
+        <is>
+          <t>En skadad knäckt men levande sälg.</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En skadad knäckt men levande sälg.</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4987,12 +4743,7 @@
         <v>122208210</v>
       </c>
       <c r="B36" t="n">
-        <v>79737</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5124,15 +4875,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122193443</v>
+        <v>122223793</v>
       </c>
       <c r="B37" t="n">
-        <v>90857</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5140,51 +4886,44 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>514671</v>
+        <v>514631</v>
       </c>
       <c r="R37" t="n">
-        <v>7023306</v>
+        <v>7023229</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5216,12 +4955,18 @@
           <t>2025-01-18</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ett par "knippen" med lunglav på en grovbarkad sälg.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5230,24 +4975,34 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
+        </is>
+      </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL37" t="inlineStr">
+        <is>
+          <t>En något smalare men grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En något smalare men grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5265,15 +5020,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122191658</v>
+        <v>122663511</v>
       </c>
       <c r="B38" t="n">
-        <v>78656</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5281,34 +5031,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>514512</v>
+        <v>514749</v>
       </c>
       <c r="R38" t="n">
-        <v>7023275</v>
+        <v>7023284</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5335,12 +5090,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5354,27 +5109,27 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5392,15 +5147,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122208128</v>
+        <v>122667349</v>
       </c>
       <c r="B39" t="n">
-        <v>79737</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5426,26 +5176,24 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
           <t>med soral</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>514240</v>
+        <v>514253</v>
       </c>
       <c r="R39" t="n">
-        <v>7023172</v>
+        <v>7023302</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5469,17 +5217,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ymnig påväxt av lunglav på sälg.</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5488,18 +5231,12 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>Med inslag av gran, sälg och björk.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
@@ -5512,11 +5249,6 @@
           <t>Salix caprea</t>
         </is>
       </c>
-      <c r="AL39" t="inlineStr">
-        <is>
-          <t>En skadad knäckt men levande sälg.</t>
-        </is>
-      </c>
       <c r="AM39" t="inlineStr">
         <is>
           <t>Bark på levande träd</t>
@@ -5524,7 +5256,7 @@
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En skadad knäckt men levande sälg.</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5542,64 +5274,52 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122193236</v>
+        <v>121667143</v>
       </c>
       <c r="B40" t="n">
-        <v>57536</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>514622</v>
+        <v>514636</v>
       </c>
       <c r="R40" t="n">
-        <v>7023310</v>
+        <v>7023234</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5626,12 +5346,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5640,12 +5360,38 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5663,61 +5409,53 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122208320</v>
+        <v>121670799</v>
       </c>
       <c r="B41" t="n">
-        <v>57399</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>514264</v>
+        <v>514265</v>
       </c>
       <c r="R41" t="n">
-        <v>7023177</v>
+        <v>7023278</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5741,17 +5479,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Färska hackspår av spillkråka i en sälg.</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5768,11 +5501,6 @@
           <t>Tallskog</t>
         </is>
       </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>Med inslag av gran, sälg och björk.</t>
-        </is>
-      </c>
       <c r="AJ41" t="inlineStr">
         <is>
           <t>sälg</t>
@@ -5785,12 +5513,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Stem on living tree # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5808,65 +5536,51 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122207795</v>
+        <v>121667163</v>
       </c>
       <c r="B42" t="n">
-        <v>57383</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sauholmen, Klenflon, Häggenås, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>514641</v>
+        <v>514636</v>
       </c>
       <c r="R42" t="n">
-        <v>7023370</v>
+        <v>7023234</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5890,17 +5604,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Färska hackspår (ringhack), i basen av en gran, som bedöms vara skapade inom 5 år tillbaks. I området kring denna plats finns även födosökspår på stående smala döda granar.</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5909,37 +5618,38 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Grandominerad skog med inslag av tall och björk på frisk-fuktig och fuktig mark.</t>
+          <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5957,50 +5667,52 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122192869</v>
+        <v>121667243</v>
       </c>
       <c r="B43" t="n">
-        <v>78656</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>514655</v>
+        <v>514636</v>
       </c>
       <c r="R43" t="n">
-        <v>7023373</v>
+        <v>7023234</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6027,12 +5739,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2024-12-19</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6041,6 +5758,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -6049,24 +5767,34 @@
           <t>Barrskog</t>
         </is>
       </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
+        </is>
+      </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL43" t="inlineStr">
+        <is>
+          <t>En gammal tvåstammig delvis skadad sälg.</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En gammal tvåstammig delvis skadad sälg.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6084,53 +5812,55 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122194308</v>
+        <v>121666620</v>
       </c>
       <c r="B44" t="n">
-        <v>78656</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>514604</v>
+        <v>514538</v>
       </c>
       <c r="R44" t="n">
-        <v>7023237</v>
+        <v>7023126</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6157,12 +5887,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6171,7 +5901,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6180,11 +5909,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
-        </is>
-      </c>
       <c r="AJ44" t="inlineStr">
         <is>
           <t>gran</t>
@@ -6197,12 +5921,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6220,60 +5944,60 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122194394</v>
+        <v>122208029</v>
       </c>
       <c r="B45" t="n">
-        <v>79738</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Lillberget, Klenflon, Häggenås, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>514600</v>
+        <v>514232</v>
       </c>
       <c r="R45" t="n">
-        <v>7023243</v>
+        <v>7023309</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6307,7 +6031,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>Färska rejäla hackspår av spillkråka i basen av en gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6316,43 +6040,37 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
+          <t>Äldre skog med olikåldriga träd.</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL45" t="inlineStr">
-        <is>
-          <t>En smal skadad knäckt sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Grov bark. # Salix caprea # En smal skadad knäckt sälg.</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6370,57 +6088,53 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122223793</v>
+        <v>122208320</v>
       </c>
       <c r="B46" t="n">
-        <v>79737</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sauholmen, Jmt</t>
+          <t>Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>514631</v>
+        <v>514264</v>
       </c>
       <c r="R46" t="n">
-        <v>7023229</v>
+        <v>7023177</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -6457,7 +6171,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ett par "knippen" med lunglav på en grovbarkad sälg.</t>
+          <t>Färska hackspår av spillkråka i en sälg.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6466,18 +6180,17 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
+          <t>Med inslag av gran, sälg och björk.</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
@@ -6490,19 +6203,14 @@
           <t>Salix caprea</t>
         </is>
       </c>
-      <c r="AL46" t="inlineStr">
-        <is>
-          <t>En något smalare men grovbarkad sälg.</t>
-        </is>
-      </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea # En något smalare men grovbarkad sälg.</t>
+          <t>Stem on living tree # Salix caprea</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6520,32 +6228,27 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122194568</v>
+        <v>122223410</v>
       </c>
       <c r="B47" t="n">
-        <v>57383</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -6558,7 +6261,7 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -6568,17 +6271,17 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Klenflon, Häggenås, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>514580</v>
+        <v>514617</v>
       </c>
       <c r="R47" t="n">
-        <v>7023243</v>
+        <v>7023224</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6612,7 +6315,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Äldre ringhack på basen av en gran.</t>
+          <t>Relativt nyligen använt bohål på ca 4 meters höjd i en delvis skadad och hålig asp.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6636,12 +6339,17 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AL47" t="inlineStr">
+        <is>
+          <t>En asp med uppskattningvis minst 30 cm i brösthöjdsdiameter. I trädets stam finns även fler håligheter och en uthackad skada i trädets stambas.</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
@@ -6651,7 +6359,7 @@
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Populus tremula # En asp med uppskattningvis minst 30 cm i brösthöjdsdiameter. I trädets stam finns även fler håligheter och en uthackad skada i trädets stambas.</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6669,15 +6377,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122226624</v>
+        <v>121669055</v>
       </c>
       <c r="B48" t="n">
-        <v>78656</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6685,40 +6388,45 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>514188</v>
+        <v>514434</v>
       </c>
       <c r="R48" t="n">
-        <v>7023245</v>
+        <v>7023259</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6742,17 +6450,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Garnlav på flera granar.</t>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6761,18 +6469,17 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Äldre barrskog med en mosaik av talldominerade och grandominerade partier på frisk till fuktig mark.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk till fuktig mark. Här finns både stående och liggande död ved.</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -6787,12 +6494,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6810,15 +6517,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122226449</v>
+        <v>121669062</v>
       </c>
       <c r="B49" t="n">
-        <v>78656</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6826,40 +6528,45 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lillberget, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514425</v>
+        <v>514434</v>
       </c>
       <c r="R49" t="n">
-        <v>7023228</v>
+        <v>7023257</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6883,17 +6590,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på flera granar.</t>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6902,7 +6609,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6913,7 +6619,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>Grandominerad gammal skog med olikåldriga träd på frisk till fuktig mark. Här finns både stående och liggande död ved. Kolade stubbar indikerar tidigare brandpåverkan.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk till fuktig mark. Här finns både stående och liggande död ved.</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -6928,12 +6634,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6951,15 +6657,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122193783</v>
+        <v>121669887</v>
       </c>
       <c r="B50" t="n">
-        <v>79737</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6967,41 +6668,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514670</v>
+        <v>514428</v>
       </c>
       <c r="R50" t="n">
-        <v>7023247</v>
+        <v>7023241</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7028,17 +6730,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>Äldre ringhack på gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7047,43 +6749,37 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
+          <t>Grandominerad gammal skog med olikåldriga träd på frisk till fuktig mark. Här finns både stående och liggande död ved.</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL50" t="inlineStr">
-        <is>
-          <t>En knäckt smal relativt grovbarkad sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En knäckt smal relativt grovbarkad sälg.</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7101,15 +6797,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122223410</v>
+        <v>121671072</v>
       </c>
       <c r="B51" t="n">
-        <v>57494</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -7117,16 +6808,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -7135,31 +6826,24 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sauholmen, Klenflon, Häggenås, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>514617</v>
+        <v>514232</v>
       </c>
       <c r="R51" t="n">
-        <v>7023224</v>
+        <v>7023294</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7183,17 +6867,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Relativt nyligen använt bohål på ca 4 meters höjd i en delvis skadad och hålig asp.</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7204,41 +6883,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AL51" t="inlineStr">
-        <is>
-          <t>En asp med uppskattningvis minst 30 cm i brösthöjdsdiameter. I trädets stam finns även fler håligheter och en uthackad skada i trädets stambas.</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Populus tremula # En asp med uppskattningvis minst 30 cm i brösthöjdsdiameter. I trädets stam finns även fler håligheter och en uthackad skada i trädets stambas.</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -7255,55 +6899,57 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122662456</v>
+        <v>122194568</v>
       </c>
       <c r="B52" t="n">
-        <v>56688</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>hona</t>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lillberget, Klenflon, Häggenås, Jmt</t>
+          <t>Lillberget, Lillberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>514349</v>
+        <v>514580</v>
       </c>
       <c r="R52" t="n">
-        <v>7023392</v>
+        <v>7023243</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7330,12 +6976,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2025-01-18</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på basen av en gran.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7346,6 +6997,36 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Barrdominerad skog med gran, tall och inslag av sälg, asp och björk på frisk och frisk-fuktig mark. Olikåldriga träd och viss mängd stående och liggande död ved. Större block finns här och där i denna skog.</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -7362,15 +7043,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122667349</v>
+        <v>122207795</v>
       </c>
       <c r="B53" t="n">
-        <v>79847</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7378,42 +7054,49 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Klenflon, Häggenås, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>514253</v>
+        <v>514641</v>
       </c>
       <c r="R53" t="n">
-        <v>7023302</v>
+        <v>7023370</v>
       </c>
       <c r="S53" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7437,12 +7120,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2025-01-18</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Färska hackspår (ringhack), i basen av en gran, som bedöms vara skapade inom 5 år tillbaks. I området kring denna plats finns även födosökspår på stående smala döda granar.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7459,24 +7147,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall och björk på frisk-fuktig och fuktig mark.</t>
+        </is>
+      </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7494,55 +7187,50 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122663511</v>
+        <v>122662456</v>
       </c>
       <c r="B54" t="n">
-        <v>79847</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sauholmen, Sauholmen, Jmt</t>
+          <t>Lillberget, Klenflon, Häggenås, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>514749</v>
+        <v>514349</v>
       </c>
       <c r="R54" t="n">
-        <v>7023284</v>
+        <v>7023392</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7585,31 +7273,6 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -7626,15 +7289,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122662245</v>
+        <v>122193236</v>
       </c>
       <c r="B55" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7642,34 +7300,48 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lillberget, Lillberget, Jmt</t>
+          <t>Sauholmen, Sauholmen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>514347</v>
+        <v>514622</v>
       </c>
       <c r="R55" t="n">
-        <v>7023344</v>
+        <v>7023310</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7696,12 +7368,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7712,6 +7384,11 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7725,108 +7402,6 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>122662339</v>
-      </c>
-      <c r="B56" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>Lillberget, Lillberget, Jmt</t>
-        </is>
-      </c>
-      <c r="Q56" t="n">
-        <v>514345</v>
-      </c>
-      <c r="R56" t="n">
-        <v>7023366</v>
-      </c>
-      <c r="S56" t="n">
-        <v>10</v>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>Häggenås</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>2025-02-18</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>2025-02-18</t>
-        </is>
-      </c>
-      <c r="AD56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT56" t="inlineStr"/>
-      <c r="AW56" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55314-2024 artfynd.xlsx
+++ b/artfynd/A 55314-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AZ55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -817,6 +822,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121667142</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121670773</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1041,6 +1056,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121670797</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1138,6 +1158,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121671169</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1283,6 +1308,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122194394</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1405,6 +1435,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121666824</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1527,6 +1562,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121666863</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1649,6 +1689,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121667138</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1771,6 +1816,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121667545</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1893,6 +1943,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121668309</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2015,6 +2070,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121668931</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2137,6 +2197,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121669034</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2259,6 +2324,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121669094</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2381,6 +2451,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121671163</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2503,6 +2578,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122191658</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2625,6 +2705,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122192869</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2756,6 +2841,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122194308</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2892,6 +2982,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122226449</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3028,6 +3123,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122226624</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3125,6 +3225,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122662245</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3222,6 +3327,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122662339</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3344,6 +3454,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122663546</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3489,6 +3604,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121667141</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3586,6 +3706,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121667649</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3683,6 +3808,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121670504</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3780,6 +3910,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121670575</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3902,6 +4037,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121670753</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3999,6 +4139,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121670772</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4126,6 +4271,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121671097</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4253,6 +4403,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121671125</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4350,6 +4505,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121671149</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4447,6 +4607,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121671167</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4592,6 +4757,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122193783</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4737,6 +4907,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122208128</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4872,6 +5047,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122208210</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5017,6 +5197,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122223793</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5144,6 +5329,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122663511</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5271,6 +5461,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122667349</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5406,6 +5601,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121667143</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5533,6 +5733,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121670799</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5664,6 +5869,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121667163</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5809,6 +6019,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121667243</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5941,6 +6156,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121666620</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6085,6 +6305,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122208029</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6225,6 +6450,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122208320</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6374,6 +6604,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122223410</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6514,6 +6749,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121669055</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6654,6 +6894,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121669062</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6794,6 +7039,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121669887</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6896,6 +7146,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121671072</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -7040,6 +7295,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122194568</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7184,6 +7444,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122207795</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7286,6 +7551,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122662456</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7402,8 +7672,69 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122193236</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>